--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="832">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -692,6 +692,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -785,8 +788,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -5508,10 +5511,10 @@
         <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5586,7 +5589,7 @@
         <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>79</v>
@@ -5597,10 +5600,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5715,10 +5718,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5833,10 +5836,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5862,13 +5865,13 @@
         <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5876,7 +5879,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>79</v>
@@ -5918,7 +5921,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -5953,10 +5956,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5979,13 +5982,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6036,7 +6039,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -6045,7 +6048,7 @@
         <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>103</v>
@@ -6071,10 +6074,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6189,10 +6192,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6283,7 +6286,7 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
@@ -6298,7 +6301,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -6309,10 +6312,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6335,16 +6338,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6394,7 +6397,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6403,22 +6406,22 @@
         <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -6429,10 +6432,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6455,23 +6458,23 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>79</v>
@@ -6516,7 +6519,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6525,22 +6528,22 @@
         <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -6551,13 +6554,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -6579,13 +6582,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6671,13 +6674,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -6699,13 +6702,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6771,7 +6774,7 @@
         <v>120</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -6791,13 +6794,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>79</v>
@@ -6819,13 +6822,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6894,7 +6897,7 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -6911,13 +6914,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -6939,13 +6942,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7011,10 +7014,10 @@
         <v>120</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -7031,13 +7034,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -7059,13 +7062,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7134,7 +7137,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -7151,13 +7154,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -7179,13 +7182,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7271,10 +7274,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7300,16 +7303,16 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -7358,7 +7361,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7393,10 +7396,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7419,17 +7422,17 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7466,10 +7469,10 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
@@ -7478,7 +7481,7 @@
         <v>118</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7487,7 +7490,7 @@
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7499,27 +7502,27 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -7541,17 +7544,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -7600,7 +7603,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7609,36 +7612,36 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7753,10 +7756,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7873,10 +7876,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7902,16 +7905,16 @@
         <v>176</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7921,7 +7924,7 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>79</v>
@@ -7936,13 +7939,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -7960,7 +7963,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7984,7 +7987,7 @@
         <v>199</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7995,10 +7998,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8021,19 +8024,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -8043,7 +8046,7 @@
         <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>79</v>
@@ -8061,10 +8064,10 @@
         <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -8082,7 +8085,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8103,10 +8106,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -8117,10 +8120,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8146,16 +8149,16 @@
         <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -8165,10 +8168,10 @@
         <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>79</v>
@@ -8204,7 +8207,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8225,13 +8228,13 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -8239,10 +8242,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8268,13 +8271,13 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8288,7 +8291,7 @@
         <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>79</v>
@@ -8324,7 +8327,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8345,13 +8348,13 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -8359,10 +8362,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8385,13 +8388,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8442,7 +8445,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8463,13 +8466,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -8477,10 +8480,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8503,16 +8506,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8562,7 +8565,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8583,13 +8586,13 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -8597,13 +8600,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -8625,17 +8628,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8684,7 +8687,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8693,36 +8696,36 @@
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8837,10 +8840,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8957,10 +8960,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8986,16 +8989,16 @@
         <v>176</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -9020,13 +9023,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -9044,7 +9047,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9068,7 +9071,7 @@
         <v>199</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -9079,10 +9082,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9105,19 +9108,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -9145,10 +9148,10 @@
         <v>158</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -9166,7 +9169,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9187,10 +9190,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -9201,10 +9204,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9319,10 +9322,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9439,10 +9442,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9468,16 +9471,16 @@
         <v>154</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9526,7 +9529,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9547,10 +9550,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9561,10 +9564,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9679,10 +9682,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9799,10 +9802,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9828,16 +9831,16 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9847,7 +9850,7 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>79</v>
@@ -9886,7 +9889,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9907,10 +9910,10 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9921,10 +9924,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9950,13 +9953,13 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10006,7 +10009,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -10027,10 +10030,10 @@
         <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -10041,10 +10044,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10070,14 +10073,14 @@
         <v>176</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -10126,7 +10129,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10147,10 +10150,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -10161,10 +10164,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10190,14 +10193,14 @@
         <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -10246,7 +10249,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10267,10 +10270,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -10281,10 +10284,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10307,19 +10310,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -10368,7 +10371,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10389,10 +10392,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -10403,10 +10406,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10432,16 +10435,16 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10490,7 +10493,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10511,10 +10514,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -10525,10 +10528,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10554,16 +10557,16 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -10573,10 +10576,10 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>79</v>
@@ -10612,7 +10615,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10633,13 +10636,13 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -10647,10 +10650,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10676,13 +10679,13 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10696,7 +10699,7 @@
         <v>79</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>79</v>
@@ -10732,7 +10735,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10753,13 +10756,13 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10767,10 +10770,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10793,13 +10796,13 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10850,7 +10853,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10871,13 +10874,13 @@
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10885,10 +10888,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10911,16 +10914,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10970,7 +10973,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10991,13 +10994,13 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -11005,13 +11008,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -11033,17 +11036,17 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -11092,7 +11095,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11101,36 +11104,36 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11245,10 +11248,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11365,10 +11368,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11394,16 +11397,16 @@
         <v>176</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -11428,13 +11431,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -11452,7 +11455,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11476,7 +11479,7 @@
         <v>199</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -11487,10 +11490,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11513,19 +11516,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -11553,10 +11556,10 @@
         <v>158</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -11574,7 +11577,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11595,10 +11598,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -11609,10 +11612,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11727,10 +11730,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11847,10 +11850,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11876,16 +11879,16 @@
         <v>154</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11934,7 +11937,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11955,10 +11958,10 @@
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11969,10 +11972,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12087,10 +12090,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12207,10 +12210,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12236,16 +12239,16 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -12255,7 +12258,7 @@
         <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>79</v>
@@ -12294,7 +12297,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12315,10 +12318,10 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -12329,10 +12332,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12358,13 +12361,13 @@
         <v>105</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12414,7 +12417,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12435,10 +12438,10 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -12449,10 +12452,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12478,14 +12481,14 @@
         <v>176</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -12534,7 +12537,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12555,10 +12558,10 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -12569,10 +12572,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12598,14 +12601,14 @@
         <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -12654,7 +12657,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12675,10 +12678,10 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -12689,10 +12692,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12715,19 +12718,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12776,7 +12779,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12797,10 +12800,10 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12811,10 +12814,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12840,16 +12843,16 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12898,7 +12901,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12919,10 +12922,10 @@
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12933,10 +12936,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12962,16 +12965,16 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12981,10 +12984,10 @@
         <v>79</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>79</v>
@@ -13020,7 +13023,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -13041,13 +13044,13 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -13055,10 +13058,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13084,13 +13087,13 @@
         <v>105</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13104,7 +13107,7 @@
         <v>79</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>79</v>
@@ -13140,7 +13143,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13161,13 +13164,13 @@
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>79</v>
@@ -13175,10 +13178,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13201,13 +13204,13 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13258,7 +13261,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13279,13 +13282,13 @@
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>79</v>
@@ -13293,10 +13296,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13319,16 +13322,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13378,7 +13381,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13399,13 +13402,13 @@
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -13413,13 +13416,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13441,17 +13444,17 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -13500,7 +13503,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13509,7 +13512,7 @@
         <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -13521,24 +13524,24 @@
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13653,10 +13656,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13773,10 +13776,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13802,16 +13805,16 @@
         <v>176</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13836,13 +13839,13 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
@@ -13860,7 +13863,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13884,7 +13887,7 @@
         <v>199</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -13895,10 +13898,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13921,19 +13924,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13943,7 +13946,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -13961,10 +13964,10 @@
         <v>158</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13982,7 +13985,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -14003,10 +14006,10 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -14017,10 +14020,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14046,16 +14049,16 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -14065,10 +14068,10 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>79</v>
@@ -14104,7 +14107,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14125,13 +14128,13 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -14139,10 +14142,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14168,13 +14171,13 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14188,7 +14191,7 @@
         <v>79</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>79</v>
@@ -14224,7 +14227,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14245,13 +14248,13 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -14259,10 +14262,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14285,13 +14288,13 @@
         <v>92</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14342,7 +14345,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14363,13 +14366,13 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>79</v>
@@ -14377,10 +14380,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14403,16 +14406,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14462,7 +14465,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14483,13 +14486,13 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>79</v>
@@ -14497,13 +14500,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14525,17 +14528,17 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -14584,7 +14587,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14593,7 +14596,7 @@
         <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>103</v>
@@ -14605,24 +14608,24 @@
         <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14737,10 +14740,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14857,10 +14860,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14886,16 +14889,16 @@
         <v>176</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14920,13 +14923,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14944,7 +14947,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14968,7 +14971,7 @@
         <v>199</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14979,10 +14982,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15005,19 +15008,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -15027,7 +15030,7 @@
         <v>79</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>79</v>
@@ -15045,10 +15048,10 @@
         <v>158</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
@@ -15066,7 +15069,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15087,10 +15090,10 @@
         <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -15101,10 +15104,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15130,16 +15133,16 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -15149,10 +15152,10 @@
         <v>79</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>79</v>
@@ -15188,7 +15191,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15209,13 +15212,13 @@
         <v>79</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>79</v>
@@ -15223,10 +15226,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15252,13 +15255,13 @@
         <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15272,7 +15275,7 @@
         <v>79</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>79</v>
@@ -15308,7 +15311,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15329,13 +15332,13 @@
         <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>79</v>
@@ -15343,10 +15346,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15369,13 +15372,13 @@
         <v>92</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15426,7 +15429,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15447,13 +15450,13 @@
         <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15461,10 +15464,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15487,16 +15490,16 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15546,7 +15549,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15567,13 +15570,13 @@
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>79</v>
@@ -15581,10 +15584,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15607,70 +15610,70 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q106" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="R106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="R106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15688,27 +15691,27 @@
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15731,19 +15734,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15771,16 +15774,16 @@
         <v>166</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15790,7 +15793,7 @@
         <v>118</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15811,27 +15814,27 @@
         <v>79</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>79</v>
@@ -15853,19 +15856,19 @@
         <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15890,11 +15893,11 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -15912,7 +15915,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15933,24 +15936,24 @@
         <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16065,10 +16068,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16183,13 +16186,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>547</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>79</v>
@@ -16211,13 +16214,13 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16303,10 +16306,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16421,10 +16424,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16513,7 +16516,7 @@
         <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>120</v>
@@ -16539,10 +16542,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16568,13 +16571,13 @@
         <v>138</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16582,7 +16585,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>79</v>
@@ -16624,7 +16627,7 @@
         <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>91</v>
@@ -16659,10 +16662,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16688,10 +16691,10 @@
         <v>176</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16703,7 +16706,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16718,11 +16721,11 @@
         <v>79</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>79</v>
@@ -16740,7 +16743,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16749,7 +16752,7 @@
         <v>91</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>103</v>
@@ -16775,10 +16778,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16804,16 +16807,16 @@
         <v>154</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16862,7 +16865,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16883,10 +16886,10 @@
         <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>79</v>
@@ -16897,10 +16900,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17015,10 +17018,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17135,10 +17138,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17164,16 +17167,16 @@
         <v>138</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17222,7 +17225,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17243,10 +17246,10 @@
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -17257,10 +17260,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17286,13 +17289,13 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17342,7 +17345,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17363,10 +17366,10 @@
         <v>79</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>79</v>
@@ -17377,10 +17380,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17406,14 +17409,14 @@
         <v>176</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -17462,7 +17465,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17483,10 +17486,10 @@
         <v>79</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>79</v>
@@ -17497,10 +17500,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17526,14 +17529,14 @@
         <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -17582,7 +17585,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17603,10 +17606,10 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17617,10 +17620,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17643,19 +17646,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -17704,7 +17707,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17725,10 +17728,10 @@
         <v>79</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17739,10 +17742,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17768,16 +17771,16 @@
         <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17826,7 +17829,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17847,10 +17850,10 @@
         <v>79</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>79</v>
@@ -17861,13 +17864,13 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>79</v>
@@ -17889,19 +17892,19 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17926,11 +17929,11 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>79</v>
@@ -17948,7 +17951,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17969,24 +17972,24 @@
         <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18101,10 +18104,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18221,10 +18224,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18250,16 +18253,16 @@
         <v>154</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -18308,7 +18311,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18329,10 +18332,10 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>79</v>
@@ -18343,10 +18346,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18461,10 +18464,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18581,10 +18584,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18610,16 +18613,16 @@
         <v>138</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18668,7 +18671,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18689,10 +18692,10 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18703,10 +18706,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18732,13 +18735,13 @@
         <v>105</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18788,7 +18791,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18809,10 +18812,10 @@
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18823,10 +18826,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18852,14 +18855,14 @@
         <v>176</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18908,7 +18911,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18929,10 +18932,10 @@
         <v>79</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -18943,10 +18946,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18972,14 +18975,14 @@
         <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -19028,7 +19031,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19049,10 +19052,10 @@
         <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -19063,10 +19066,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19089,19 +19092,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -19150,7 +19153,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19171,10 +19174,10 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>79</v>
@@ -19185,10 +19188,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19214,16 +19217,16 @@
         <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19272,7 +19275,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19293,10 +19296,10 @@
         <v>79</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19307,13 +19310,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>79</v>
@@ -19335,19 +19338,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
@@ -19372,11 +19375,11 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>79</v>
@@ -19394,7 +19397,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19415,24 +19418,24 @@
         <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19547,10 +19550,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19667,10 +19670,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19696,16 +19699,16 @@
         <v>154</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -19754,7 +19757,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19775,10 +19778,10 @@
         <v>79</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>79</v>
@@ -19789,10 +19792,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19907,10 +19910,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20027,10 +20030,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20056,16 +20059,16 @@
         <v>138</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -20114,7 +20117,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20135,10 +20138,10 @@
         <v>79</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>79</v>
@@ -20149,10 +20152,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20178,13 +20181,13 @@
         <v>105</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -20234,7 +20237,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20255,10 +20258,10 @@
         <v>79</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>79</v>
@@ -20269,10 +20272,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20298,14 +20301,14 @@
         <v>176</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20354,7 +20357,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20375,10 +20378,10 @@
         <v>79</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>79</v>
@@ -20389,10 +20392,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20418,14 +20421,14 @@
         <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20474,7 +20477,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20495,10 +20498,10 @@
         <v>79</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20509,10 +20512,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20535,19 +20538,19 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20596,7 +20599,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20617,10 +20620,10 @@
         <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20631,10 +20634,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20660,16 +20663,16 @@
         <v>105</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -20718,7 +20721,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20739,10 +20742,10 @@
         <v>79</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20753,13 +20756,13 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D149" t="s" s="2">
         <v>79</v>
@@ -20781,19 +20784,19 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20818,11 +20821,11 @@
         <v>79</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>79</v>
@@ -20840,7 +20843,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20855,30 +20858,30 @@
         <v>103</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20993,10 +20996,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21085,7 +21088,7 @@
         <v>81</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>120</v>
@@ -21111,13 +21114,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -21139,13 +21142,13 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21205,7 +21208,7 @@
         <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>120</v>
@@ -21231,10 +21234,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21349,10 +21352,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21441,7 +21444,7 @@
         <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>120</v>
@@ -21467,10 +21470,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21496,13 +21499,13 @@
         <v>138</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21510,7 +21513,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>79</v>
@@ -21552,7 +21555,7 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>91</v>
@@ -21587,10 +21590,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21616,10 +21619,10 @@
         <v>176</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21631,7 +21634,7 @@
         <v>79</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>79</v>
@@ -21646,11 +21649,11 @@
         <v>79</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>79</v>
@@ -21668,7 +21671,7 @@
         <v>79</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -21677,7 +21680,7 @@
         <v>91</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>103</v>
@@ -21703,10 +21706,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21732,16 +21735,16 @@
         <v>154</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>79</v>
@@ -21790,7 +21793,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21799,7 +21802,7 @@
         <v>81</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>103</v>
@@ -21811,10 +21814,10 @@
         <v>79</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21825,10 +21828,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21854,16 +21857,16 @@
         <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21912,7 +21915,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21921,7 +21924,7 @@
         <v>91</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>103</v>
@@ -21933,10 +21936,10 @@
         <v>79</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21947,13 +21950,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>79</v>
@@ -21975,19 +21978,19 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -22012,11 +22015,11 @@
         <v>79</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>79</v>
@@ -22034,7 +22037,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22049,30 +22052,30 @@
         <v>103</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22187,10 +22190,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22279,7 +22282,7 @@
         <v>81</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>120</v>
@@ -22305,13 +22308,13 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>79</v>
@@ -22333,13 +22336,13 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22399,7 +22402,7 @@
         <v>81</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>120</v>
@@ -22425,10 +22428,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22543,10 +22546,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22635,7 +22638,7 @@
         <v>81</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>120</v>
@@ -22661,10 +22664,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22690,13 +22693,13 @@
         <v>138</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22704,7 +22707,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>79</v>
@@ -22746,7 +22749,7 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>91</v>
@@ -22781,10 +22784,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22810,10 +22813,10 @@
         <v>176</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22825,7 +22828,7 @@
         <v>79</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>79</v>
@@ -22840,11 +22843,11 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>79</v>
@@ -22862,7 +22865,7 @@
         <v>79</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -22871,7 +22874,7 @@
         <v>91</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>103</v>
@@ -22897,10 +22900,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22926,16 +22929,16 @@
         <v>154</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22984,7 +22987,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -22993,7 +22996,7 @@
         <v>81</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>103</v>
@@ -23005,10 +23008,10 @@
         <v>79</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23019,10 +23022,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23048,16 +23051,16 @@
         <v>105</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
@@ -23106,7 +23109,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23115,7 +23118,7 @@
         <v>91</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>103</v>
@@ -23127,10 +23130,10 @@
         <v>79</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23141,13 +23144,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>79</v>
@@ -23169,19 +23172,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
@@ -23206,11 +23209,11 @@
         <v>79</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>79</v>
@@ -23228,7 +23231,7 @@
         <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23246,27 +23249,27 @@
         <v>79</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23381,10 +23384,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23473,7 +23476,7 @@
         <v>81</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>120</v>
@@ -23499,13 +23502,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>79</v>
@@ -23527,13 +23530,13 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23593,7 +23596,7 @@
         <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>120</v>
@@ -23619,10 +23622,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23737,10 +23740,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23829,7 +23832,7 @@
         <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>120</v>
@@ -23855,10 +23858,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23884,13 +23887,13 @@
         <v>138</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23898,7 +23901,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>79</v>
@@ -23940,7 +23943,7 @@
         <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>91</v>
@@ -23975,10 +23978,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24004,10 +24007,10 @@
         <v>176</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24019,7 +24022,7 @@
         <v>79</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>79</v>
@@ -24034,11 +24037,11 @@
         <v>79</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>79</v>
@@ -24056,7 +24059,7 @@
         <v>79</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -24065,7 +24068,7 @@
         <v>91</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>103</v>
@@ -24091,10 +24094,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24120,16 +24123,16 @@
         <v>154</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>79</v>
@@ -24178,7 +24181,7 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24187,7 +24190,7 @@
         <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>103</v>
@@ -24199,10 +24202,10 @@
         <v>79</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>79</v>
@@ -24213,10 +24216,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24242,16 +24245,16 @@
         <v>105</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>79</v>
@@ -24300,7 +24303,7 @@
         <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24309,7 +24312,7 @@
         <v>91</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>103</v>
@@ -24321,10 +24324,10 @@
         <v>79</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24335,13 +24338,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>79</v>
@@ -24363,19 +24366,19 @@
         <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -24403,10 +24406,10 @@
         <v>166</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>79</v>
@@ -24424,7 +24427,7 @@
         <v>79</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24445,24 +24448,24 @@
         <v>79</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24577,10 +24580,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24669,7 +24672,7 @@
         <v>81</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>120</v>
@@ -24695,13 +24698,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>79</v>
@@ -24723,13 +24726,13 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24789,7 +24792,7 @@
         <v>81</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>120</v>
@@ -24815,10 +24818,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24933,10 +24936,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25025,7 +25028,7 @@
         <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>120</v>
@@ -25051,10 +25054,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25080,13 +25083,13 @@
         <v>138</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -25094,7 +25097,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>79</v>
@@ -25136,7 +25139,7 @@
         <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>91</v>
@@ -25171,10 +25174,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25200,10 +25203,10 @@
         <v>176</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25215,7 +25218,7 @@
         <v>79</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>79</v>
@@ -25230,11 +25233,11 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>79</v>
@@ -25252,7 +25255,7 @@
         <v>79</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25261,7 +25264,7 @@
         <v>91</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>103</v>
@@ -25287,10 +25290,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25316,16 +25319,16 @@
         <v>154</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
@@ -25374,7 +25377,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25383,7 +25386,7 @@
         <v>81</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>103</v>
@@ -25395,10 +25398,10 @@
         <v>79</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25409,10 +25412,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25438,16 +25441,16 @@
         <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>79</v>
@@ -25496,7 +25499,7 @@
         <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25505,7 +25508,7 @@
         <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>103</v>
@@ -25517,10 +25520,10 @@
         <v>79</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25531,10 +25534,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25560,16 +25563,16 @@
         <v>105</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>79</v>
@@ -25618,7 +25621,7 @@
         <v>79</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -25627,25 +25630,25 @@
         <v>91</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>79</v>
@@ -25653,10 +25656,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25682,16 +25685,16 @@
         <v>105</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>79</v>
@@ -25740,7 +25743,7 @@
         <v>79</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -25755,16 +25758,16 @@
         <v>103</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>79</v>
@@ -25775,10 +25778,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25801,19 +25804,19 @@
         <v>79</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>79</v>
@@ -25850,7 +25853,7 @@
         <v>79</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AC191" s="2"/>
       <c r="AD191" t="s" s="2">
@@ -25860,7 +25863,7 @@
         <v>118</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -25872,22 +25875,22 @@
         <v>208</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>79</v>
@@ -25895,10 +25898,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26013,10 +26016,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26133,13 +26136,13 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="B194" t="s" s="2">
-        <v>697</v>
-      </c>
       <c r="C194" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D194" t="s" s="2">
         <v>79</v>
@@ -26161,13 +26164,13 @@
         <v>79</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -26253,10 +26256,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26282,10 +26285,10 @@
         <v>176</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26312,13 +26315,13 @@
         <v>79</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>79</v>
@@ -26336,7 +26339,7 @@
         <v>79</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26345,7 +26348,7 @@
         <v>91</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>103</v>
@@ -26357,13 +26360,13 @@
         <v>79</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AO195" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AP195" t="s" s="2">
         <v>79</v>
@@ -26371,10 +26374,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26400,16 +26403,16 @@
         <v>105</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>79</v>
@@ -26458,7 +26461,7 @@
         <v>79</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26479,13 +26482,13 @@
         <v>79</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>79</v>
@@ -26493,10 +26496,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26522,16 +26525,16 @@
         <v>176</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>79</v>
@@ -26556,13 +26559,13 @@
         <v>79</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>79</v>
@@ -26580,7 +26583,7 @@
         <v>79</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26601,13 +26604,13 @@
         <v>79</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AP197" t="s" s="2">
         <v>79</v>
@@ -26615,10 +26618,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26641,16 +26644,16 @@
         <v>92</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26700,7 +26703,7 @@
         <v>79</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -26735,10 +26738,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26761,13 +26764,13 @@
         <v>92</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26818,7 +26821,7 @@
         <v>79</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -26842,10 +26845,10 @@
         <v>199</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>79</v>
@@ -26853,13 +26856,13 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D200" t="s" s="2">
         <v>79</v>
@@ -26881,19 +26884,19 @@
         <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>79</v>
@@ -26942,7 +26945,7 @@
         <v>79</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -26954,22 +26957,22 @@
         <v>208</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>79</v>
@@ -26977,10 +26980,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27003,19 +27006,19 @@
         <v>79</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>79</v>
@@ -27064,7 +27067,7 @@
         <v>79</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -27076,22 +27079,22 @@
         <v>208</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>79</v>
@@ -27099,10 +27102,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27125,17 +27128,17 @@
         <v>92</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>79</v>
@@ -27184,7 +27187,7 @@
         <v>79</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -27205,10 +27208,10 @@
         <v>79</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>109</v>
@@ -27219,10 +27222,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27337,10 +27340,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27457,10 +27460,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27486,13 +27489,13 @@
         <v>105</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27542,7 +27545,7 @@
         <v>79</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -27551,7 +27554,7 @@
         <v>91</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AJ205" t="s" s="2">
         <v>103</v>
@@ -27577,10 +27580,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27606,13 +27609,13 @@
         <v>138</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -27642,7 +27645,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>79</v>
@@ -27660,7 +27663,7 @@
         <v>79</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -27695,10 +27698,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27721,16 +27724,16 @@
         <v>92</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -27780,7 +27783,7 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27804,7 +27807,7 @@
         <v>79</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>79</v>
@@ -27815,10 +27818,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27844,13 +27847,13 @@
         <v>105</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27900,7 +27903,7 @@
         <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -27935,10 +27938,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27961,19 +27964,19 @@
         <v>79</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>79</v>
@@ -28022,7 +28025,7 @@
         <v>79</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -28046,7 +28049,7 @@
         <v>79</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>79</v>
@@ -28057,10 +28060,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28175,10 +28178,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28295,14 +28298,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -28324,16 +28327,16 @@
         <v>112</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="N212" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>79</v>
@@ -28382,7 +28385,7 @@
         <v>79</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -28417,10 +28420,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28443,17 +28446,17 @@
         <v>79</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>79</v>
@@ -28481,10 +28484,10 @@
         <v>158</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>79</v>
@@ -28502,7 +28505,7 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28526,7 +28529,7 @@
         <v>79</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>79</v>
@@ -28537,10 +28540,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28563,17 +28566,17 @@
         <v>79</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>79</v>
@@ -28622,7 +28625,7 @@
         <v>79</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -28643,10 +28646,10 @@
         <v>79</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>79</v>
@@ -28657,10 +28660,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28683,17 +28686,17 @@
         <v>79</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>79</v>
@@ -28742,7 +28745,7 @@
         <v>79</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -28754,7 +28757,7 @@
         <v>208</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>79</v>
@@ -28763,13 +28766,13 @@
         <v>79</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>79</v>
@@ -28777,10 +28780,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28803,19 +28806,19 @@
         <v>79</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>79</v>
@@ -28864,7 +28867,7 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -28885,13 +28888,13 @@
         <v>79</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>79</v>
@@ -28899,10 +28902,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28925,17 +28928,17 @@
         <v>79</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>79</v>
@@ -28984,7 +28987,7 @@
         <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="839">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -792,10 +792,10 @@
 per-1</t>
   </si>
   <si>
-    <t>dateCreation</t>
-  </si>
-  <si>
-    <t>dateOuverture</t>
+    <t>EntiteJuridique.dateCreation</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.dateOuverture</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -825,7 +825,10 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateFermeture</t>
+    <t>EntiteJuridique.dateFermeture</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.dateFermeture</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -866,7 +869,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la licence d’exploitation d’une officine.</t>
   </si>
   <si>
-    <t>numeroLicenceOfficine</t>
+    <t>EntiteJuridique.numeroLicenceOfficine</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-pricing-model</t>
@@ -885,7 +888,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du mode de tarification de la structure.</t>
   </si>
   <si>
-    <t>modeFixationTarifaire</t>
+    <t>EntiteGeographique.modeFixationTarifaire</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-closing-type</t>
@@ -904,7 +907,10 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du type de fermeture de la structure.</t>
   </si>
   <si>
-    <t>typeFermeture</t>
+    <t>EntiteJuridique.typeFermeture</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.typeFermeture</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-budget-type</t>
@@ -923,7 +929,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la nature du budget alloué à la structure.</t>
   </si>
   <si>
-    <t>natureEtablissement</t>
+    <t>EntiteGeographique.natureEtablissement</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-authorization-deadline</t>
@@ -1006,7 +1012,10 @@
     <t>Identifiant idNat_Struct délivré par une autorité d'enregistrement tel que défini dans l'Annexe Transverse Source des données métier pour les professionnels et les structures.</t>
   </si>
   <si>
-    <t>idNat_struct</t>
+    <t>EntiteJuridique.idNat_struct</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.idNat_struct</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.id</t>
@@ -1229,7 +1238,10 @@
     <t>Identifiant SIREN (9 chiffres) ou SIRET (14 chiffres)</t>
   </si>
   <si>
-    <t>numSiren</t>
+    <t>EntiteJuridique.numSiren</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.numSiren</t>
   </si>
   <si>
     <t>Organization.identifier:sirene.id</t>
@@ -1482,7 +1494,10 @@
     <t>Identifiant FINESS Entité Géographique (EG) ou Entité Juridique (EJ)</t>
   </si>
   <si>
-    <t>numFiness</t>
+    <t>EntiteJuridique.numFiness</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.numFiness</t>
   </si>
   <si>
     <t>Organization.identifier:finess.id</t>
@@ -1647,7 +1662,7 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
-    <t>actif</t>
+    <t>EntiteGeographique.actif</t>
   </si>
   <si>
     <t>No equivalent in HL7 v2</t>
@@ -1933,10 +1948,10 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
   </si>
   <si>
-    <t>codeAPEN</t>
-  </si>
-  <si>
-    <t>codeAPET</t>
+    <t>EntiteJuridique.codeAPEN</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.codeAPET</t>
   </si>
   <si>
     <t>Organization.type:activiteINSEE.id</t>
@@ -1978,7 +1993,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
   </si>
   <si>
-    <t>statutJuridique</t>
+    <t>EntiteJuridique.statutJuridique</t>
   </si>
   <si>
     <t>Organization.type:statutJuridiqueINSEE.id</t>
@@ -2098,10 +2113,10 @@
     <t>Need to use the name as the label of the organization.</t>
   </si>
   <si>
-    <t>raisonSociale</t>
-  </si>
-  <si>
-    <t>denominationEG</t>
+    <t>EntiteJuridique.raisonSociale</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.denominationEG</t>
   </si>
   <si>
     <t>XON.1</t>
@@ -2129,10 +2144,10 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
-    <t>raisonSocialeLongue</t>
-  </si>
-  <si>
-    <t>denominationEGLongue</t>
+    <t>EntiteJuridique.raisonSocialeLongue</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.denominationEGLongue</t>
   </si>
   <si>
     <t>Organization.telecom</t>
@@ -2162,7 +2177,10 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>telecommunication</t>
+    <t>EntiteJuridique.telecommunication</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.telecommunication</t>
   </si>
   <si>
     <t>XTN</t>
@@ -2331,7 +2349,10 @@
     <t>Les BALs MSS de type ORG ou APP rattachées à une personne morale responsable de l’accès et de l’usage de la BAL (boiteLettreMSS).</t>
   </si>
   <si>
-    <t>boiteLettreMSS</t>
+    <t>EntiteJuridique.boiteLettreMSS</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.boiteLettreMSS</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -2357,10 +2378,10 @@
 org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>adresseEJ</t>
-  </si>
-  <si>
-    <t>adresseEG</t>
+    <t>EntiteJuridique.adresseEJ</t>
+  </si>
+  <si>
+    <t>EntiteGeographique.adresseEG</t>
   </si>
   <si>
     <t>XAD</t>
@@ -2951,7 +2972,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="39.41015625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="40.23046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="42.02734375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="218.1953125" customWidth="true" bestFit="true"/>
@@ -6537,13 +6558,13 @@
         <v>259</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -6554,13 +6575,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>79</v>
@@ -6582,13 +6603,13 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6674,13 +6695,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>79</v>
@@ -6702,13 +6723,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6774,7 +6795,7 @@
         <v>120</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
@@ -6794,13 +6815,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>79</v>
@@ -6822,13 +6843,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6897,7 +6918,7 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -6914,13 +6935,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>79</v>
@@ -6942,13 +6963,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -7014,10 +7035,10 @@
         <v>120</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -7034,13 +7055,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>79</v>
@@ -7062,13 +7083,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7137,7 +7158,7 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
@@ -7154,13 +7175,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>200</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
@@ -7182,13 +7203,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7274,10 +7295,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7303,16 +7324,16 @@
         <v>112</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -7361,7 +7382,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7396,10 +7417,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7422,17 +7443,17 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -7469,10 +7490,10 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
@@ -7481,7 +7502,7 @@
         <v>118</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7490,7 +7511,7 @@
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>103</v>
@@ -7502,27 +7523,27 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>79</v>
@@ -7544,17 +7565,17 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -7603,7 +7624,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7612,36 +7633,36 @@
         <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7756,10 +7777,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7876,10 +7897,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7905,16 +7926,16 @@
         <v>176</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7924,7 +7945,7 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>79</v>
@@ -7939,13 +7960,13 @@
         <v>79</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -7963,7 +7984,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7987,7 +8008,7 @@
         <v>199</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7998,10 +8019,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8024,19 +8045,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -8046,7 +8067,7 @@
         <v>79</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>79</v>
@@ -8064,10 +8085,10 @@
         <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -8085,7 +8106,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -8106,10 +8127,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -8120,10 +8141,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8149,16 +8170,16 @@
         <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -8168,10 +8189,10 @@
         <v>79</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>79</v>
@@ -8207,7 +8228,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -8228,13 +8249,13 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -8242,10 +8263,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8271,13 +8292,13 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8291,7 +8312,7 @@
         <v>79</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>79</v>
@@ -8327,7 +8348,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8348,13 +8369,13 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -8362,10 +8383,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8391,10 +8412,10 @@
         <v>231</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8445,7 +8466,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8466,13 +8487,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -8480,10 +8501,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8506,16 +8527,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8565,7 +8586,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8586,13 +8607,13 @@
         <v>79</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -8600,13 +8621,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -8628,17 +8649,17 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -8687,7 +8708,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8696,36 +8717,36 @@
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8840,10 +8861,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8960,10 +8981,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8989,16 +9010,16 @@
         <v>176</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -9023,13 +9044,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -9047,7 +9068,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -9071,7 +9092,7 @@
         <v>199</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -9082,10 +9103,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9108,19 +9129,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -9148,10 +9169,10 @@
         <v>158</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -9169,7 +9190,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -9190,10 +9211,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -9204,10 +9225,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9322,10 +9343,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9442,10 +9463,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9471,16 +9492,16 @@
         <v>154</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -9529,7 +9550,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9550,10 +9571,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -9564,10 +9585,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9682,10 +9703,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9802,10 +9823,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9831,16 +9852,16 @@
         <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -9850,7 +9871,7 @@
         <v>79</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>79</v>
@@ -9889,7 +9910,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9910,10 +9931,10 @@
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9924,10 +9945,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9953,13 +9974,13 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10009,7 +10030,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -10030,10 +10051,10 @@
         <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -10044,10 +10065,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10073,14 +10094,14 @@
         <v>176</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -10129,7 +10150,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -10150,10 +10171,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -10164,10 +10185,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10193,14 +10214,14 @@
         <v>105</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -10249,7 +10270,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10270,10 +10291,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -10284,10 +10305,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10310,19 +10331,19 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -10371,7 +10392,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10392,10 +10413,10 @@
         <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -10406,10 +10427,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10435,16 +10456,16 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -10493,7 +10514,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10514,10 +10535,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -10528,10 +10549,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10557,16 +10578,16 @@
         <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -10576,10 +10597,10 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>79</v>
@@ -10615,7 +10636,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10636,13 +10657,13 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -10650,10 +10671,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10679,13 +10700,13 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10699,7 +10720,7 @@
         <v>79</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>79</v>
@@ -10735,7 +10756,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10756,13 +10777,13 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -10770,10 +10791,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10799,10 +10820,10 @@
         <v>231</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10853,7 +10874,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10874,13 +10895,13 @@
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>79</v>
@@ -10888,10 +10909,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10914,16 +10935,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10973,7 +10994,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10994,13 +11015,13 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -11008,13 +11029,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -11036,17 +11057,17 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -11095,7 +11116,7 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -11104,36 +11125,36 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11248,10 +11269,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11368,10 +11389,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11397,16 +11418,16 @@
         <v>176</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -11431,13 +11452,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -11455,7 +11476,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11479,7 +11500,7 @@
         <v>199</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -11490,10 +11511,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11516,19 +11537,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -11556,10 +11577,10 @@
         <v>158</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -11577,7 +11598,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11598,10 +11619,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -11612,10 +11633,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11730,10 +11751,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11850,10 +11871,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11879,16 +11900,16 @@
         <v>154</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11937,7 +11958,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11958,10 +11979,10 @@
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>79</v>
@@ -11972,10 +11993,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12090,10 +12111,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12210,10 +12231,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12239,16 +12260,16 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -12258,7 +12279,7 @@
         <v>79</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>79</v>
@@ -12297,7 +12318,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12318,10 +12339,10 @@
         <v>79</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
@@ -12332,10 +12353,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12361,13 +12382,13 @@
         <v>105</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12417,7 +12438,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12438,10 +12459,10 @@
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>79</v>
@@ -12452,10 +12473,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12481,14 +12502,14 @@
         <v>176</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>79</v>
@@ -12537,7 +12558,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12558,10 +12579,10 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>79</v>
@@ -12572,10 +12593,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12601,14 +12622,14 @@
         <v>105</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -12657,7 +12678,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12678,10 +12699,10 @@
         <v>79</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -12692,10 +12713,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12718,19 +12739,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -12779,7 +12800,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12800,10 +12821,10 @@
         <v>79</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -12814,10 +12835,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12843,16 +12864,16 @@
         <v>105</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>79</v>
@@ -12901,7 +12922,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12922,10 +12943,10 @@
         <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12936,10 +12957,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12965,16 +12986,16 @@
         <v>138</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
@@ -12984,10 +13005,10 @@
         <v>79</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>79</v>
@@ -13023,7 +13044,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -13044,13 +13065,13 @@
         <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>79</v>
@@ -13058,10 +13079,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13087,13 +13108,13 @@
         <v>105</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13107,7 +13128,7 @@
         <v>79</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>79</v>
@@ -13143,7 +13164,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -13164,13 +13185,13 @@
         <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>79</v>
@@ -13178,10 +13199,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13207,10 +13228,10 @@
         <v>231</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13261,7 +13282,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -13282,13 +13303,13 @@
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>79</v>
@@ -13296,10 +13317,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13322,16 +13343,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13381,7 +13402,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13402,13 +13423,13 @@
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -13416,13 +13437,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13444,17 +13465,17 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -13503,7 +13524,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13512,7 +13533,7 @@
         <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -13524,24 +13545,24 @@
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13656,10 +13677,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13776,10 +13797,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13805,16 +13826,16 @@
         <v>176</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -13839,13 +13860,13 @@
         <v>79</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>79</v>
@@ -13863,7 +13884,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13887,7 +13908,7 @@
         <v>199</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>79</v>
@@ -13898,10 +13919,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13924,19 +13945,19 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>79</v>
@@ -13946,7 +13967,7 @@
         <v>79</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>79</v>
@@ -13964,10 +13985,10 @@
         <v>158</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13985,7 +14006,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -14006,10 +14027,10 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>79</v>
@@ -14020,10 +14041,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14049,16 +14070,16 @@
         <v>138</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -14068,10 +14089,10 @@
         <v>79</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>79</v>
@@ -14107,7 +14128,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -14128,13 +14149,13 @@
         <v>79</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -14142,10 +14163,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14171,13 +14192,13 @@
         <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -14191,7 +14212,7 @@
         <v>79</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>79</v>
@@ -14227,7 +14248,7 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -14248,13 +14269,13 @@
         <v>79</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>79</v>
@@ -14262,10 +14283,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14291,10 +14312,10 @@
         <v>231</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14345,7 +14366,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14366,13 +14387,13 @@
         <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>79</v>
@@ -14380,10 +14401,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14406,16 +14427,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14465,7 +14486,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14486,13 +14507,13 @@
         <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>79</v>
@@ -14500,13 +14521,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>79</v>
@@ -14528,17 +14549,17 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
@@ -14587,7 +14608,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14596,7 +14617,7 @@
         <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>103</v>
@@ -14608,24 +14629,24 @@
         <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14740,10 +14761,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14860,10 +14881,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14889,16 +14910,16 @@
         <v>176</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -14923,13 +14944,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -14947,7 +14968,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14971,7 +14992,7 @@
         <v>199</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14982,10 +15003,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15008,19 +15029,19 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>79</v>
@@ -15030,7 +15051,7 @@
         <v>79</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>79</v>
@@ -15048,10 +15069,10 @@
         <v>158</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
@@ -15069,7 +15090,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -15090,10 +15111,10 @@
         <v>79</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>79</v>
@@ -15104,10 +15125,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15133,16 +15154,16 @@
         <v>138</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>79</v>
@@ -15152,10 +15173,10 @@
         <v>79</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>79</v>
@@ -15191,7 +15212,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -15212,13 +15233,13 @@
         <v>79</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>79</v>
@@ -15226,10 +15247,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15255,13 +15276,13 @@
         <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -15275,7 +15296,7 @@
         <v>79</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>79</v>
@@ -15311,7 +15332,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15332,13 +15353,13 @@
         <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>79</v>
@@ -15346,10 +15367,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15375,10 +15396,10 @@
         <v>231</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15429,7 +15450,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15450,13 +15471,13 @@
         <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -15464,10 +15485,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15490,16 +15511,16 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15549,7 +15570,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15570,13 +15591,13 @@
         <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>79</v>
@@ -15584,10 +15605,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15610,70 +15631,70 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q106" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="R106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="R106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15691,27 +15712,27 @@
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15734,19 +15755,19 @@
         <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -15774,16 +15795,16 @@
         <v>166</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15793,7 +15814,7 @@
         <v>118</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15814,27 +15835,27 @@
         <v>79</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>79</v>
@@ -15856,19 +15877,19 @@
         <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>79</v>
@@ -15893,11 +15914,11 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -15915,7 +15936,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15936,24 +15957,24 @@
         <v>79</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16068,10 +16089,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16186,13 +16207,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>79</v>
@@ -16214,13 +16235,13 @@
         <v>79</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16306,10 +16327,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16424,10 +16445,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16542,10 +16563,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16585,7 +16606,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>79</v>
@@ -16662,10 +16683,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16694,7 +16715,7 @@
         <v>232</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16706,7 +16727,7 @@
         <v>79</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>79</v>
@@ -16721,11 +16742,11 @@
         <v>79</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>79</v>
@@ -16778,10 +16799,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16807,16 +16828,16 @@
         <v>154</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>79</v>
@@ -16865,7 +16886,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16886,10 +16907,10 @@
         <v>79</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>79</v>
@@ -16900,10 +16921,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17018,10 +17039,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17138,10 +17159,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17167,16 +17188,16 @@
         <v>138</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -17225,7 +17246,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -17246,10 +17267,10 @@
         <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>79</v>
@@ -17260,10 +17281,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17289,13 +17310,13 @@
         <v>105</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -17345,7 +17366,7 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17366,10 +17387,10 @@
         <v>79</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>79</v>
@@ -17380,10 +17401,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17409,14 +17430,14 @@
         <v>176</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -17465,7 +17486,7 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17486,10 +17507,10 @@
         <v>79</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>79</v>
@@ -17500,10 +17521,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17529,14 +17550,14 @@
         <v>105</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
@@ -17585,7 +17606,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17606,10 +17627,10 @@
         <v>79</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>79</v>
@@ -17620,10 +17641,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17646,19 +17667,19 @@
         <v>92</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -17707,7 +17728,7 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17728,10 +17749,10 @@
         <v>79</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>79</v>
@@ -17742,10 +17763,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17771,16 +17792,16 @@
         <v>105</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
@@ -17829,7 +17850,7 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17850,10 +17871,10 @@
         <v>79</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>79</v>
@@ -17864,13 +17885,13 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>79</v>
@@ -17892,19 +17913,19 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>79</v>
@@ -17929,11 +17950,11 @@
         <v>79</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>79</v>
@@ -17951,7 +17972,7 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17972,24 +17993,24 @@
         <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18104,10 +18125,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18224,10 +18245,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18253,16 +18274,16 @@
         <v>154</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>79</v>
@@ -18311,7 +18332,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18332,10 +18353,10 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>79</v>
@@ -18346,10 +18367,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18464,10 +18485,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18584,10 +18605,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18613,16 +18634,16 @@
         <v>138</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>79</v>
@@ -18671,7 +18692,7 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18692,10 +18713,10 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18706,10 +18727,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18735,13 +18756,13 @@
         <v>105</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18791,7 +18812,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18812,10 +18833,10 @@
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18826,10 +18847,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18855,14 +18876,14 @@
         <v>176</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18911,7 +18932,7 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18932,10 +18953,10 @@
         <v>79</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -18946,10 +18967,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18975,14 +18996,14 @@
         <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>79</v>
@@ -19031,7 +19052,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19052,10 +19073,10 @@
         <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -19066,10 +19087,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19092,19 +19113,19 @@
         <v>92</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>79</v>
@@ -19153,7 +19174,7 @@
         <v>79</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -19174,10 +19195,10 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>79</v>
@@ -19188,10 +19209,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19217,16 +19238,16 @@
         <v>105</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19275,7 +19296,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19296,10 +19317,10 @@
         <v>79</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19310,13 +19331,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>79</v>
@@ -19338,19 +19359,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>79</v>
@@ -19375,11 +19396,11 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>79</v>
@@ -19397,7 +19418,7 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19418,24 +19439,24 @@
         <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19550,10 +19571,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19670,10 +19691,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19699,16 +19720,16 @@
         <v>154</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -19757,7 +19778,7 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19778,10 +19799,10 @@
         <v>79</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>79</v>
@@ -19792,10 +19813,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19910,10 +19931,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20030,10 +20051,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20059,16 +20080,16 @@
         <v>138</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>79</v>
@@ -20117,7 +20138,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20138,10 +20159,10 @@
         <v>79</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>79</v>
@@ -20152,10 +20173,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20181,13 +20202,13 @@
         <v>105</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -20237,7 +20258,7 @@
         <v>79</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -20258,10 +20279,10 @@
         <v>79</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>79</v>
@@ -20272,10 +20293,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20301,14 +20322,14 @@
         <v>176</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20357,7 +20378,7 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -20378,10 +20399,10 @@
         <v>79</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>79</v>
@@ -20392,10 +20413,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20421,14 +20442,14 @@
         <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>79</v>
@@ -20477,7 +20498,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20498,10 +20519,10 @@
         <v>79</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20512,10 +20533,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20538,19 +20559,19 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>79</v>
@@ -20599,7 +20620,7 @@
         <v>79</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -20620,10 +20641,10 @@
         <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20634,10 +20655,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20663,16 +20684,16 @@
         <v>105</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -20721,7 +20742,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20742,10 +20763,10 @@
         <v>79</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20756,13 +20777,13 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="D149" t="s" s="2">
         <v>79</v>
@@ -20784,19 +20805,19 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>79</v>
@@ -20821,11 +20842,11 @@
         <v>79</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>79</v>
@@ -20843,7 +20864,7 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -20858,30 +20879,30 @@
         <v>103</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20996,10 +21017,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21114,13 +21135,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -21142,13 +21163,13 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21234,10 +21255,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21352,10 +21373,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21470,10 +21491,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21513,7 +21534,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>79</v>
@@ -21590,10 +21611,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21622,7 +21643,7 @@
         <v>232</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21634,7 +21655,7 @@
         <v>79</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>79</v>
@@ -21649,11 +21670,11 @@
         <v>79</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>79</v>
@@ -21706,10 +21727,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21735,16 +21756,16 @@
         <v>154</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>79</v>
@@ -21793,7 +21814,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21814,10 +21835,10 @@
         <v>79</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21828,10 +21849,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21857,16 +21878,16 @@
         <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>79</v>
@@ -21915,7 +21936,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21936,10 +21957,10 @@
         <v>79</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21950,13 +21971,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>79</v>
@@ -21978,19 +21999,19 @@
         <v>92</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>79</v>
@@ -22015,11 +22036,11 @@
         <v>79</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>79</v>
@@ -22037,7 +22058,7 @@
         <v>79</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22052,30 +22073,30 @@
         <v>103</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22190,10 +22211,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22308,13 +22329,13 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>79</v>
@@ -22336,13 +22357,13 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22428,10 +22449,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22546,10 +22567,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22664,10 +22685,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22707,7 +22728,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>79</v>
@@ -22784,10 +22805,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22816,7 +22837,7 @@
         <v>232</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22828,7 +22849,7 @@
         <v>79</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>79</v>
@@ -22843,11 +22864,11 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>79</v>
@@ -22900,10 +22921,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22929,16 +22950,16 @@
         <v>154</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>79</v>
@@ -22987,7 +23008,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -23008,10 +23029,10 @@
         <v>79</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23022,10 +23043,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23051,16 +23072,16 @@
         <v>105</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>79</v>
@@ -23109,7 +23130,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23130,10 +23151,10 @@
         <v>79</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23144,13 +23165,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>79</v>
@@ -23172,19 +23193,19 @@
         <v>92</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>79</v>
@@ -23209,11 +23230,11 @@
         <v>79</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>79</v>
@@ -23231,7 +23252,7 @@
         <v>79</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23249,27 +23270,27 @@
         <v>79</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23384,10 +23405,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23502,13 +23523,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>79</v>
@@ -23530,13 +23551,13 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23622,10 +23643,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23740,10 +23761,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23858,10 +23879,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23901,7 +23922,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>79</v>
@@ -23978,10 +23999,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24010,7 +24031,7 @@
         <v>232</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24022,7 +24043,7 @@
         <v>79</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>79</v>
@@ -24037,11 +24058,11 @@
         <v>79</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>79</v>
@@ -24094,10 +24115,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24123,16 +24144,16 @@
         <v>154</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>79</v>
@@ -24181,7 +24202,7 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24202,10 +24223,10 @@
         <v>79</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>79</v>
@@ -24216,10 +24237,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24245,16 +24266,16 @@
         <v>105</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>79</v>
@@ -24303,7 +24324,7 @@
         <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24324,10 +24345,10 @@
         <v>79</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24338,13 +24359,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>79</v>
@@ -24366,19 +24387,19 @@
         <v>92</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -24406,28 +24427,28 @@
         <v>166</v>
       </c>
       <c r="Y179" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF179" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24448,24 +24469,24 @@
         <v>79</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24580,10 +24601,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24698,13 +24719,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>79</v>
@@ -24726,13 +24747,13 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24818,10 +24839,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24936,10 +24957,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25054,10 +25075,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25097,7 +25118,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>79</v>
@@ -25174,10 +25195,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25206,7 +25227,7 @@
         <v>232</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25218,7 +25239,7 @@
         <v>79</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>79</v>
@@ -25233,11 +25254,11 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>79</v>
@@ -25290,10 +25311,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25319,16 +25340,16 @@
         <v>154</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
@@ -25377,7 +25398,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25398,10 +25419,10 @@
         <v>79</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25412,10 +25433,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25441,16 +25462,16 @@
         <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>79</v>
@@ -25499,7 +25520,7 @@
         <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25520,10 +25541,10 @@
         <v>79</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25534,10 +25555,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25563,16 +25584,16 @@
         <v>105</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>79</v>
@@ -25621,7 +25642,7 @@
         <v>79</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -25630,25 +25651,25 @@
         <v>91</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>79</v>
@@ -25656,10 +25677,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25685,16 +25706,16 @@
         <v>105</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>79</v>
@@ -25743,7 +25764,7 @@
         <v>79</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -25758,16 +25779,16 @@
         <v>103</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>79</v>
@@ -25778,10 +25799,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25804,19 +25825,19 @@
         <v>79</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>79</v>
@@ -25853,7 +25874,7 @@
         <v>79</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="AC191" s="2"/>
       <c r="AD191" t="s" s="2">
@@ -25863,7 +25884,7 @@
         <v>118</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -25875,22 +25896,22 @@
         <v>208</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>79</v>
@@ -25898,10 +25919,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26016,10 +26037,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26136,13 +26157,13 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="D194" t="s" s="2">
         <v>79</v>
@@ -26164,13 +26185,13 @@
         <v>79</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -26256,10 +26277,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26285,10 +26306,10 @@
         <v>176</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -26315,13 +26336,13 @@
         <v>79</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>79</v>
@@ -26339,7 +26360,7 @@
         <v>79</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26348,7 +26369,7 @@
         <v>91</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>103</v>
@@ -26360,13 +26381,13 @@
         <v>79</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="AO195" t="s" s="2">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="AP195" t="s" s="2">
         <v>79</v>
@@ -26374,10 +26395,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26403,16 +26424,16 @@
         <v>105</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>79</v>
@@ -26461,7 +26482,7 @@
         <v>79</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26482,13 +26503,13 @@
         <v>79</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>79</v>
@@ -26496,10 +26517,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26525,16 +26546,16 @@
         <v>176</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>79</v>
@@ -26559,13 +26580,13 @@
         <v>79</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>79</v>
@@ -26583,7 +26604,7 @@
         <v>79</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26604,13 +26625,13 @@
         <v>79</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="AP197" t="s" s="2">
         <v>79</v>
@@ -26618,10 +26639,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26644,16 +26665,16 @@
         <v>92</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26703,7 +26724,7 @@
         <v>79</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -26738,10 +26759,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26767,10 +26788,10 @@
         <v>231</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26821,7 +26842,7 @@
         <v>79</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -26845,10 +26866,10 @@
         <v>199</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>79</v>
@@ -26856,13 +26877,13 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="D200" t="s" s="2">
         <v>79</v>
@@ -26884,19 +26905,19 @@
         <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>79</v>
@@ -26945,7 +26966,7 @@
         <v>79</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -26957,22 +26978,22 @@
         <v>208</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>79</v>
@@ -26980,10 +27001,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27006,19 +27027,19 @@
         <v>79</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>79</v>
@@ -27067,7 +27088,7 @@
         <v>79</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -27079,22 +27100,22 @@
         <v>208</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>79</v>
@@ -27102,10 +27123,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27128,17 +27149,17 @@
         <v>92</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>79</v>
@@ -27187,7 +27208,7 @@
         <v>79</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -27208,10 +27229,10 @@
         <v>79</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>109</v>
@@ -27222,10 +27243,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27340,10 +27361,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27460,10 +27481,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27489,13 +27510,13 @@
         <v>105</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -27545,7 +27566,7 @@
         <v>79</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -27554,7 +27575,7 @@
         <v>91</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="AJ205" t="s" s="2">
         <v>103</v>
@@ -27580,10 +27601,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27609,13 +27630,13 @@
         <v>138</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -27645,7 +27666,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>79</v>
@@ -27663,7 +27684,7 @@
         <v>79</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -27698,10 +27719,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27724,16 +27745,16 @@
         <v>92</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -27783,7 +27804,7 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27807,7 +27828,7 @@
         <v>79</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>79</v>
@@ -27818,10 +27839,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27847,13 +27868,13 @@
         <v>105</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27903,7 +27924,7 @@
         <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -27938,10 +27959,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27964,19 +27985,19 @@
         <v>79</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>79</v>
@@ -28025,7 +28046,7 @@
         <v>79</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -28049,7 +28070,7 @@
         <v>79</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>79</v>
@@ -28060,10 +28081,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28178,10 +28199,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28298,14 +28319,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -28327,16 +28348,16 @@
         <v>112</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="N212" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>79</v>
@@ -28385,7 +28406,7 @@
         <v>79</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -28420,10 +28441,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28446,17 +28467,17 @@
         <v>79</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" t="s" s="2">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>79</v>
@@ -28484,10 +28505,10 @@
         <v>158</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>79</v>
@@ -28505,7 +28526,7 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28529,7 +28550,7 @@
         <v>79</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>79</v>
@@ -28540,10 +28561,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28566,17 +28587,17 @@
         <v>79</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>79</v>
@@ -28625,7 +28646,7 @@
         <v>79</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -28646,10 +28667,10 @@
         <v>79</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>79</v>
@@ -28660,10 +28681,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28686,17 +28707,17 @@
         <v>79</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>79</v>
@@ -28745,7 +28766,7 @@
         <v>79</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -28757,7 +28778,7 @@
         <v>208</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>79</v>
@@ -28766,13 +28787,13 @@
         <v>79</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>79</v>
@@ -28780,10 +28801,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28806,19 +28827,19 @@
         <v>79</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>79</v>
@@ -28867,7 +28888,7 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -28888,13 +28909,13 @@
         <v>79</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>79</v>
@@ -28902,10 +28923,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28928,17 +28949,17 @@
         <v>79</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>831</v>
+        <v>838</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>79</v>
@@ -28987,7 +29008,7 @@
         <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$222</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8294" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8479" uniqueCount="844">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1861,6 +1861,21 @@
   </si>
   <si>
     <t>Organization.type:secteurActiviteRASS.extension</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.id</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.extension</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.url</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.value[x]</t>
   </si>
   <si>
     <t>Organization.type:secteurActiviteRASS.coding</t>
@@ -2933,7 +2948,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP217"/>
+  <dimension ref="A1:AP222"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -18132,11 +18147,11 @@
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>81</v>
@@ -18154,14 +18169,12 @@
         <v>112</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>79</v>
@@ -18234,7 +18247,7 @@
         <v>79</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>79</v>
@@ -18248,9 +18261,11 @@
         <v>595</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C128" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>79</v>
       </c>
@@ -18268,23 +18283,19 @@
         <v>79</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>154</v>
+        <v>556</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>403</v>
+        <v>557</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>79</v>
       </c>
@@ -18332,7 +18343,7 @@
         <v>79</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>407</v>
+        <v>119</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18344,7 +18355,7 @@
         <v>79</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>79</v>
@@ -18353,10 +18364,10 @@
         <v>79</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>408</v>
+        <v>79</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>79</v>
@@ -18370,7 +18381,7 @@
         <v>596</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18488,18 +18499,18 @@
         <v>597</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>79</v>
@@ -18514,14 +18525,12 @@
         <v>112</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>79</v>
@@ -18579,7 +18588,7 @@
         <v>81</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>120</v>
@@ -18594,7 +18603,7 @@
         <v>79</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>79</v>
@@ -18608,7 +18617,7 @@
         <v>598</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18628,29 +18637,27 @@
         <v>79</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>416</v>
+        <v>224</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>417</v>
+        <v>225</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>79</v>
+        <v>565</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>79</v>
@@ -18692,10 +18699,10 @@
         <v>79</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>421</v>
+        <v>228</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>91</v>
@@ -18704,7 +18711,7 @@
         <v>79</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>79</v>
@@ -18713,10 +18720,10 @@
         <v>79</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>423</v>
+        <v>199</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>79</v>
@@ -18730,7 +18737,7 @@
         <v>599</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18750,20 +18757,18 @@
         <v>79</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>426</v>
+        <v>232</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>79</v>
@@ -18773,7 +18778,7 @@
         <v>79</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>79</v>
+        <v>590</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>79</v>
@@ -18788,13 +18793,11 @@
         <v>79</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>79</v>
+        <v>569</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>79</v>
@@ -18812,7 +18815,7 @@
         <v>79</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>429</v>
+        <v>234</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18821,7 +18824,7 @@
         <v>91</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>103</v>
@@ -18833,10 +18836,10 @@
         <v>79</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>430</v>
+        <v>79</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>431</v>
+        <v>199</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>79</v>
@@ -18850,7 +18853,7 @@
         <v>600</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18858,7 +18861,7 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>91</v>
@@ -18873,17 +18876,19 @@
         <v>92</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>582</v>
+        <v>403</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O133" t="s" s="2">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>79</v>
@@ -18932,13 +18937,13 @@
         <v>79</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>79</v>
@@ -18953,10 +18958,10 @@
         <v>79</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>79</v>
@@ -18970,7 +18975,7 @@
         <v>601</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18990,21 +18995,19 @@
         <v>79</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>442</v>
+        <v>106</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>443</v>
+        <v>107</v>
       </c>
       <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>444</v>
-      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>79</v>
       </c>
@@ -19052,7 +19055,7 @@
         <v>79</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>445</v>
+        <v>108</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -19064,7 +19067,7 @@
         <v>79</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>79</v>
@@ -19073,10 +19076,10 @@
         <v>79</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>446</v>
+        <v>79</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>447</v>
+        <v>109</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>79</v>
@@ -19090,18 +19093,18 @@
         <v>602</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>79</v>
@@ -19110,23 +19113,21 @@
         <v>79</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>450</v>
+        <v>112</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>452</v>
+        <v>114</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>79</v>
       </c>
@@ -19162,31 +19163,31 @@
         <v>79</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>455</v>
+        <v>119</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>79</v>
@@ -19195,10 +19196,10 @@
         <v>79</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>456</v>
+        <v>79</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>457</v>
+        <v>109</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>79</v>
@@ -19212,7 +19213,7 @@
         <v>603</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19220,7 +19221,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>91</v>
@@ -19235,19 +19236,19 @@
         <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>462</v>
+        <v>418</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>79</v>
@@ -19296,7 +19297,7 @@
         <v>79</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>464</v>
+        <v>421</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19317,10 +19318,10 @@
         <v>79</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>465</v>
+        <v>422</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>79</v>
@@ -19334,11 +19335,9 @@
         <v>604</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>605</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>79</v>
       </c>
@@ -19359,20 +19358,18 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>338</v>
+        <v>105</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>606</v>
+        <v>426</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>537</v>
+        <v>427</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>79</v>
       </c>
@@ -19396,11 +19393,13 @@
         <v>79</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y137" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z137" t="s" s="2">
-        <v>607</v>
+        <v>79</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>79</v>
@@ -19418,13 +19417,13 @@
         <v>79</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>535</v>
+        <v>429</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>79</v>
@@ -19439,24 +19438,24 @@
         <v>79</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>543</v>
+        <v>430</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>544</v>
+        <v>431</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AP137" t="s" s="2">
-        <v>545</v>
+        <v>79</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19476,19 +19475,21 @@
         <v>79</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>106</v>
+        <v>582</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>107</v>
+        <v>435</v>
       </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>79</v>
       </c>
@@ -19536,7 +19537,7 @@
         <v>79</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>108</v>
+        <v>437</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19548,7 +19549,7 @@
         <v>79</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>79</v>
@@ -19557,10 +19558,10 @@
         <v>79</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>79</v>
+        <v>438</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>109</v>
+        <v>439</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>79</v>
@@ -19571,21 +19572,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>79</v>
@@ -19594,21 +19595,21 @@
         <v>79</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>113</v>
+        <v>442</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O139" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>79</v>
       </c>
@@ -19644,31 +19645,31 @@
         <v>79</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>119</v>
+        <v>445</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>79</v>
@@ -19677,10 +19678,10 @@
         <v>79</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>79</v>
+        <v>446</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>109</v>
+        <v>447</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>79</v>
@@ -19691,10 +19692,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19702,7 +19703,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>91</v>
@@ -19717,19 +19718,19 @@
         <v>92</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>154</v>
+        <v>450</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>403</v>
+        <v>451</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>79</v>
@@ -19778,13 +19779,13 @@
         <v>79</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>407</v>
+        <v>455</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>79</v>
@@ -19799,10 +19800,10 @@
         <v>79</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>408</v>
+        <v>456</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>79</v>
@@ -19813,10 +19814,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19836,19 +19837,23 @@
         <v>79</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K141" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>79</v>
       </c>
@@ -19896,7 +19901,7 @@
         <v>79</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>108</v>
+        <v>464</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19908,7 +19913,7 @@
         <v>79</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>79</v>
@@ -19917,10 +19922,10 @@
         <v>79</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>109</v>
+        <v>466</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>79</v>
@@ -19931,21 +19936,23 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>610</v>
+      </c>
       <c r="D142" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>79</v>
@@ -19954,21 +19961,23 @@
         <v>79</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>112</v>
+        <v>338</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>113</v>
+        <v>611</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>114</v>
+        <v>537</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>79</v>
       </c>
@@ -19992,31 +20001,29 @@
         <v>79</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>79</v>
+        <v>612</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>119</v>
+        <v>535</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -20028,7 +20035,7 @@
         <v>79</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>79</v>
@@ -20037,16 +20044,16 @@
         <v>79</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>79</v>
+        <v>543</v>
       </c>
       <c r="AN142" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AO142" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AO142" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AP142" t="s" s="2">
-        <v>79</v>
+        <v>545</v>
       </c>
     </row>
     <row r="143" hidden="true">
@@ -20054,7 +20061,7 @@
         <v>613</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>577</v>
+        <v>551</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20062,7 +20069,7 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>91</v>
@@ -20074,23 +20081,19 @@
         <v>79</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>416</v>
+        <v>106</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>79</v>
       </c>
@@ -20138,7 +20141,7 @@
         <v>79</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>421</v>
+        <v>108</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -20150,7 +20153,7 @@
         <v>79</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>79</v>
@@ -20159,10 +20162,10 @@
         <v>79</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>422</v>
+        <v>79</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>423</v>
+        <v>109</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>79</v>
@@ -20176,18 +20179,18 @@
         <v>614</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>79</v>
@@ -20196,19 +20199,19 @@
         <v>79</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>426</v>
+        <v>113</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>427</v>
+        <v>114</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>428</v>
+        <v>115</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -20246,31 +20249,31 @@
         <v>79</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>429</v>
+        <v>119</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>79</v>
@@ -20279,10 +20282,10 @@
         <v>79</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>430</v>
+        <v>79</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>431</v>
+        <v>109</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>79</v>
@@ -20296,7 +20299,7 @@
         <v>615</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20304,7 +20307,7 @@
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>91</v>
@@ -20319,17 +20322,19 @@
         <v>92</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>582</v>
+        <v>403</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N145" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O145" t="s" s="2">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>79</v>
@@ -20378,13 +20383,13 @@
         <v>79</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>79</v>
@@ -20399,10 +20404,10 @@
         <v>79</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>79</v>
@@ -20416,7 +20421,7 @@
         <v>616</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20436,21 +20441,19 @@
         <v>79</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>442</v>
+        <v>106</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>443</v>
+        <v>107</v>
       </c>
       <c r="N146" s="2"/>
-      <c r="O146" t="s" s="2">
-        <v>444</v>
-      </c>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>79</v>
       </c>
@@ -20498,7 +20501,7 @@
         <v>79</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>445</v>
+        <v>108</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -20510,7 +20513,7 @@
         <v>79</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>79</v>
@@ -20519,10 +20522,10 @@
         <v>79</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>446</v>
+        <v>79</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>447</v>
+        <v>109</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>79</v>
@@ -20536,18 +20539,18 @@
         <v>617</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>79</v>
@@ -20556,23 +20559,21 @@
         <v>79</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>450</v>
+        <v>112</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>452</v>
+        <v>114</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>79</v>
       </c>
@@ -20608,31 +20609,31 @@
         <v>79</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>455</v>
+        <v>119</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>79</v>
@@ -20641,10 +20642,10 @@
         <v>79</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>456</v>
+        <v>79</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>457</v>
+        <v>109</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>79</v>
@@ -20658,7 +20659,7 @@
         <v>618</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20666,7 +20667,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>91</v>
@@ -20681,19 +20682,19 @@
         <v>92</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>460</v>
+        <v>416</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>462</v>
+        <v>418</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>79</v>
@@ -20742,7 +20743,7 @@
         <v>79</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>464</v>
+        <v>421</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -20763,10 +20764,10 @@
         <v>79</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>465</v>
+        <v>422</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>79</v>
@@ -20780,11 +20781,9 @@
         <v>619</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>620</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>79</v>
       </c>
@@ -20805,20 +20804,18 @@
         <v>92</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>338</v>
+        <v>105</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>621</v>
+        <v>426</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>537</v>
+        <v>427</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>79</v>
       </c>
@@ -20842,11 +20839,13 @@
         <v>79</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y149" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z149" t="s" s="2">
-        <v>622</v>
+        <v>79</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>79</v>
@@ -20864,13 +20863,13 @@
         <v>79</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>535</v>
+        <v>429</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>79</v>
@@ -20879,30 +20878,30 @@
         <v>103</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>623</v>
+        <v>79</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>624</v>
+        <v>79</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>543</v>
+        <v>430</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>544</v>
+        <v>431</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AP149" t="s" s="2">
-        <v>545</v>
+        <v>79</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20922,19 +20921,21 @@
         <v>79</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>106</v>
+        <v>582</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>107</v>
+        <v>435</v>
       </c>
       <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
+      <c r="O150" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>79</v>
       </c>
@@ -20982,7 +20983,7 @@
         <v>79</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>108</v>
+        <v>437</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -20994,7 +20995,7 @@
         <v>79</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>79</v>
@@ -21003,10 +21004,10 @@
         <v>79</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>79</v>
+        <v>438</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>109</v>
+        <v>439</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>79</v>
@@ -21017,10 +21018,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21028,10 +21029,10 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>79</v>
@@ -21040,19 +21041,21 @@
         <v>79</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>201</v>
+        <v>442</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>202</v>
+        <v>443</v>
       </c>
       <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
+      <c r="O151" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>79</v>
       </c>
@@ -21088,31 +21091,31 @@
         <v>79</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>119</v>
+        <v>445</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>79</v>
@@ -21121,10 +21124,10 @@
         <v>79</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>79</v>
+        <v>446</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>79</v>
@@ -21135,20 +21138,18 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>555</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
         <v>91</v>
@@ -21160,19 +21161,23 @@
         <v>79</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>556</v>
+        <v>450</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>557</v>
+        <v>451</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>79</v>
       </c>
@@ -21220,19 +21225,19 @@
         <v>79</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>119</v>
+        <v>455</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>79</v>
@@ -21241,10 +21246,10 @@
         <v>79</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>79</v>
+        <v>456</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>79</v>
+        <v>457</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>79</v>
@@ -21255,10 +21260,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21278,19 +21283,23 @@
         <v>79</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K153" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>79</v>
       </c>
@@ -21338,7 +21347,7 @@
         <v>79</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>108</v>
+        <v>464</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -21350,7 +21359,7 @@
         <v>79</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>79</v>
@@ -21359,10 +21368,10 @@
         <v>79</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>109</v>
+        <v>466</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>79</v>
@@ -21373,12 +21382,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C154" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="D154" t="s" s="2">
         <v>79</v>
       </c>
@@ -21387,7 +21398,7 @@
         <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>79</v>
@@ -21396,19 +21407,23 @@
         <v>79</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>112</v>
+        <v>338</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>201</v>
+        <v>626</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N154" s="2"/>
-      <c r="O154" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>79</v>
       </c>
@@ -21432,31 +21447,29 @@
         <v>79</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>79</v>
+        <v>627</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>119</v>
+        <v>535</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -21465,28 +21478,28 @@
         <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>79</v>
+        <v>628</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>79</v>
+        <v>629</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>79</v>
+        <v>543</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>79</v>
+        <v>544</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>79</v>
+        <v>545</v>
       </c>
     </row>
     <row r="155" hidden="true">
@@ -21494,7 +21507,7 @@
         <v>630</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21502,7 +21515,7 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>91</v>
@@ -21517,24 +21530,22 @@
         <v>79</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>565</v>
+        <v>79</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>79</v>
@@ -21576,10 +21587,10 @@
         <v>79</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>91</v>
@@ -21600,7 +21611,7 @@
         <v>79</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>79</v>
@@ -21614,7 +21625,7 @@
         <v>631</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21622,10 +21633,10 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>79</v>
@@ -21637,13 +21648,13 @@
         <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>568</v>
+        <v>202</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21655,7 +21666,7 @@
         <v>79</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>620</v>
+        <v>79</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>79</v>
@@ -21670,41 +21681,43 @@
         <v>79</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y156" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z156" t="s" s="2">
-        <v>569</v>
+        <v>79</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>234</v>
+        <v>119</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>79</v>
@@ -21716,7 +21729,7 @@
         <v>79</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>79</v>
@@ -21730,18 +21743,20 @@
         <v>632</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C157" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="D157" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>79</v>
@@ -21750,23 +21765,19 @@
         <v>79</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>154</v>
+        <v>556</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>403</v>
+        <v>557</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>79</v>
       </c>
@@ -21814,7 +21825,7 @@
         <v>79</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>407</v>
+        <v>119</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21826,7 +21837,7 @@
         <v>208</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>79</v>
@@ -21835,10 +21846,10 @@
         <v>79</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>408</v>
+        <v>79</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>79</v>
@@ -21852,7 +21863,7 @@
         <v>633</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21872,23 +21883,19 @@
         <v>79</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K158" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>460</v>
+        <v>106</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>79</v>
       </c>
@@ -21936,7 +21943,7 @@
         <v>79</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>464</v>
+        <v>108</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21945,10 +21952,10 @@
         <v>91</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>79</v>
@@ -21957,10 +21964,10 @@
         <v>79</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>466</v>
+        <v>109</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>79</v>
@@ -21974,11 +21981,9 @@
         <v>634</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>635</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>79</v>
       </c>
@@ -21987,7 +21992,7 @@
         <v>80</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>79</v>
@@ -21996,23 +22001,19 @@
         <v>79</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>338</v>
+        <v>112</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>636</v>
+        <v>201</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>79</v>
       </c>
@@ -22036,29 +22037,31 @@
         <v>79</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y159" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z159" t="s" s="2">
-        <v>637</v>
+        <v>79</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>535</v>
+        <v>119</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -22067,36 +22070,36 @@
         <v>81</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>638</v>
+        <v>79</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>543</v>
+        <v>79</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>544</v>
+        <v>79</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>545</v>
+        <v>79</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22104,7 +22107,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>91</v>
@@ -22119,22 +22122,24 @@
         <v>79</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N160" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q160" s="2"/>
       <c r="R160" t="s" s="2">
-        <v>79</v>
+        <v>565</v>
       </c>
       <c r="S160" t="s" s="2">
         <v>79</v>
@@ -22176,10 +22181,10 @@
         <v>79</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>91</v>
@@ -22200,7 +22205,7 @@
         <v>79</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>79</v>
@@ -22211,10 +22216,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22222,10 +22227,10 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>79</v>
@@ -22237,13 +22242,13 @@
         <v>79</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>202</v>
+        <v>568</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -22255,7 +22260,7 @@
         <v>79</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>79</v>
+        <v>625</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>79</v>
@@ -22270,43 +22275,41 @@
         <v>79</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>79</v>
+        <v>569</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>119</v>
+        <v>234</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>79</v>
@@ -22318,7 +22321,7 @@
         <v>79</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>79</v>
@@ -22329,23 +22332,21 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>555</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>79</v>
@@ -22354,19 +22355,23 @@
         <v>79</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>556</v>
+        <v>154</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>557</v>
+        <v>403</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N162" s="2"/>
-      <c r="O162" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P162" t="s" s="2">
         <v>79</v>
       </c>
@@ -22414,7 +22419,7 @@
         <v>79</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>119</v>
+        <v>407</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22426,7 +22431,7 @@
         <v>208</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>79</v>
@@ -22435,10 +22440,10 @@
         <v>79</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>79</v>
+        <v>408</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>79</v>
@@ -22449,10 +22454,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22472,19 +22477,23 @@
         <v>79</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K163" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>79</v>
       </c>
@@ -22532,7 +22541,7 @@
         <v>79</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>108</v>
+        <v>464</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22541,10 +22550,10 @@
         <v>91</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>79</v>
@@ -22553,10 +22562,10 @@
         <v>79</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>109</v>
+        <v>466</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>79</v>
@@ -22567,12 +22576,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C164" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>640</v>
+      </c>
       <c r="D164" t="s" s="2">
         <v>79</v>
       </c>
@@ -22581,7 +22592,7 @@
         <v>80</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>79</v>
@@ -22590,19 +22601,23 @@
         <v>79</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>112</v>
+        <v>338</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>201</v>
+        <v>641</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>79</v>
       </c>
@@ -22626,31 +22641,29 @@
         <v>79</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>79</v>
+        <v>642</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>119</v>
+        <v>535</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22659,28 +22672,28 @@
         <v>81</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>79</v>
+        <v>643</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>79</v>
+        <v>543</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>79</v>
+        <v>544</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>79</v>
+        <v>545</v>
       </c>
     </row>
     <row r="165" hidden="true">
@@ -22688,7 +22701,7 @@
         <v>644</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22696,7 +22709,7 @@
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
         <v>91</v>
@@ -22711,24 +22724,22 @@
         <v>79</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>565</v>
+        <v>79</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>79</v>
@@ -22770,10 +22781,10 @@
         <v>79</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>91</v>
@@ -22794,7 +22805,7 @@
         <v>79</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>79</v>
@@ -22808,7 +22819,7 @@
         <v>645</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22816,10 +22827,10 @@
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>79</v>
@@ -22831,13 +22842,13 @@
         <v>79</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>568</v>
+        <v>202</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22849,7 +22860,7 @@
         <v>79</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>635</v>
+        <v>79</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>79</v>
@@ -22864,41 +22875,43 @@
         <v>79</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y166" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z166" t="s" s="2">
-        <v>569</v>
+        <v>79</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>234</v>
+        <v>119</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>79</v>
@@ -22910,7 +22923,7 @@
         <v>79</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>79</v>
@@ -22924,18 +22937,20 @@
         <v>646</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C167" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="D167" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>79</v>
@@ -22944,23 +22959,19 @@
         <v>79</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>154</v>
+        <v>556</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>403</v>
+        <v>557</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>79</v>
       </c>
@@ -23008,7 +23019,7 @@
         <v>79</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>407</v>
+        <v>119</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -23020,7 +23031,7 @@
         <v>208</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>79</v>
@@ -23029,10 +23040,10 @@
         <v>79</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>408</v>
+        <v>79</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>79</v>
@@ -23046,7 +23057,7 @@
         <v>647</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23066,23 +23077,19 @@
         <v>79</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>460</v>
+        <v>106</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>79</v>
       </c>
@@ -23130,7 +23137,7 @@
         <v>79</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>464</v>
+        <v>108</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -23139,10 +23146,10 @@
         <v>91</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>79</v>
@@ -23151,10 +23158,10 @@
         <v>79</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>466</v>
+        <v>109</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>79</v>
@@ -23168,11 +23175,9 @@
         <v>648</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>649</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>79</v>
       </c>
@@ -23181,7 +23186,7 @@
         <v>80</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>79</v>
@@ -23190,23 +23195,19 @@
         <v>79</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>338</v>
+        <v>112</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>650</v>
+        <v>201</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>79</v>
       </c>
@@ -23230,29 +23231,31 @@
         <v>79</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y169" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z169" t="s" s="2">
-        <v>651</v>
+        <v>79</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>535</v>
+        <v>119</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -23261,36 +23264,36 @@
         <v>81</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>624</v>
+        <v>79</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>543</v>
+        <v>79</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>544</v>
+        <v>79</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AP169" t="s" s="2">
-        <v>545</v>
+        <v>79</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23298,7 +23301,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>91</v>
@@ -23313,22 +23316,24 @@
         <v>79</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N170" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>79</v>
+        <v>565</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>79</v>
@@ -23370,10 +23375,10 @@
         <v>79</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>91</v>
@@ -23394,7 +23399,7 @@
         <v>79</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>79</v>
@@ -23405,10 +23410,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23416,10 +23421,10 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>79</v>
@@ -23431,13 +23436,13 @@
         <v>79</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>202</v>
+        <v>568</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -23449,7 +23454,7 @@
         <v>79</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>79</v>
+        <v>640</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>79</v>
@@ -23464,43 +23469,41 @@
         <v>79</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y171" s="2"/>
       <c r="Z171" t="s" s="2">
-        <v>79</v>
+        <v>569</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>119</v>
+        <v>234</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>79</v>
@@ -23512,7 +23515,7 @@
         <v>79</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>79</v>
@@ -23523,23 +23526,21 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C172" t="s" s="2">
-        <v>555</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>79</v>
@@ -23548,19 +23549,23 @@
         <v>79</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>556</v>
+        <v>154</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>557</v>
+        <v>403</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N172" s="2"/>
-      <c r="O172" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P172" t="s" s="2">
         <v>79</v>
       </c>
@@ -23608,7 +23613,7 @@
         <v>79</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>119</v>
+        <v>407</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
@@ -23620,7 +23625,7 @@
         <v>208</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>79</v>
@@ -23629,10 +23634,10 @@
         <v>79</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>79</v>
+        <v>408</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>79</v>
@@ -23643,10 +23648,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23666,19 +23671,23 @@
         <v>79</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K173" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>79</v>
       </c>
@@ -23726,7 +23735,7 @@
         <v>79</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>108</v>
+        <v>464</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -23735,10 +23744,10 @@
         <v>91</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>79</v>
@@ -23747,10 +23756,10 @@
         <v>79</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>109</v>
+        <v>466</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>79</v>
@@ -23761,12 +23770,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C174" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>654</v>
+      </c>
       <c r="D174" t="s" s="2">
         <v>79</v>
       </c>
@@ -23775,7 +23786,7 @@
         <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>79</v>
@@ -23784,19 +23795,23 @@
         <v>79</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>112</v>
+        <v>338</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>201</v>
+        <v>655</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>79</v>
       </c>
@@ -23820,31 +23835,29 @@
         <v>79</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y174" s="2"/>
       <c r="Z174" t="s" s="2">
-        <v>79</v>
+        <v>656</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>119</v>
+        <v>535</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23853,28 +23866,28 @@
         <v>81</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>79</v>
+        <v>629</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>79</v>
+        <v>543</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>79</v>
+        <v>544</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AP174" t="s" s="2">
-        <v>79</v>
+        <v>545</v>
       </c>
     </row>
     <row r="175" hidden="true">
@@ -23882,7 +23895,7 @@
         <v>657</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23890,7 +23903,7 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G175" t="s" s="2">
         <v>91</v>
@@ -23905,24 +23918,22 @@
         <v>79</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>565</v>
+        <v>79</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>79</v>
@@ -23964,10 +23975,10 @@
         <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>91</v>
@@ -23988,7 +23999,7 @@
         <v>79</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>79</v>
@@ -24002,7 +24013,7 @@
         <v>658</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24010,10 +24021,10 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>79</v>
@@ -24025,13 +24036,13 @@
         <v>79</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>568</v>
+        <v>202</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -24043,7 +24054,7 @@
         <v>79</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>649</v>
+        <v>79</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>79</v>
@@ -24058,41 +24069,43 @@
         <v>79</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y176" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z176" t="s" s="2">
-        <v>569</v>
+        <v>79</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>234</v>
+        <v>119</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>79</v>
@@ -24104,7 +24117,7 @@
         <v>79</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>79</v>
@@ -24118,18 +24131,20 @@
         <v>659</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C177" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="D177" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>79</v>
@@ -24138,23 +24153,19 @@
         <v>79</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>154</v>
+        <v>556</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>403</v>
+        <v>557</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>79</v>
       </c>
@@ -24202,7 +24213,7 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>407</v>
+        <v>119</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -24214,7 +24225,7 @@
         <v>208</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>79</v>
@@ -24223,10 +24234,10 @@
         <v>79</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>408</v>
+        <v>79</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>79</v>
@@ -24240,7 +24251,7 @@
         <v>660</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24260,23 +24271,19 @@
         <v>79</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K178" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>460</v>
+        <v>106</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N178" s="2"/>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>79</v>
       </c>
@@ -24324,7 +24331,7 @@
         <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>464</v>
+        <v>108</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24333,10 +24340,10 @@
         <v>91</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>79</v>
@@ -24345,10 +24352,10 @@
         <v>79</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>466</v>
+        <v>109</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>79</v>
@@ -24362,11 +24369,9 @@
         <v>661</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>662</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>79</v>
       </c>
@@ -24375,7 +24380,7 @@
         <v>80</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>79</v>
@@ -24384,23 +24389,19 @@
         <v>79</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>338</v>
+        <v>112</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>663</v>
+        <v>201</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>79</v>
       </c>
@@ -24424,31 +24425,31 @@
         <v>79</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>540</v>
+        <v>79</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>541</v>
+        <v>79</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>535</v>
+        <v>119</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -24457,10 +24458,10 @@
         <v>81</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>79</v>
@@ -24469,24 +24470,24 @@
         <v>79</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>543</v>
+        <v>79</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>544</v>
+        <v>79</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AP179" t="s" s="2">
-        <v>545</v>
+        <v>79</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24494,7 +24495,7 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>91</v>
@@ -24509,22 +24510,24 @@
         <v>79</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N180" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>79</v>
+        <v>565</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>79</v>
@@ -24566,10 +24569,10 @@
         <v>79</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>91</v>
@@ -24590,7 +24593,7 @@
         <v>79</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>79</v>
@@ -24601,10 +24604,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24612,10 +24615,10 @@
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>79</v>
@@ -24627,13 +24630,13 @@
         <v>79</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>202</v>
+        <v>568</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -24645,7 +24648,7 @@
         <v>79</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>79</v>
+        <v>654</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>79</v>
@@ -24660,43 +24663,41 @@
         <v>79</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>79</v>
+        <v>569</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>119</v>
+        <v>234</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>79</v>
@@ -24708,7 +24709,7 @@
         <v>79</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>79</v>
@@ -24719,23 +24720,21 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C182" t="s" s="2">
-        <v>555</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>79</v>
@@ -24744,19 +24743,23 @@
         <v>79</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>556</v>
+        <v>154</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>557</v>
+        <v>403</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>79</v>
       </c>
@@ -24804,7 +24807,7 @@
         <v>79</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>119</v>
+        <v>407</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -24816,7 +24819,7 @@
         <v>208</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>79</v>
@@ -24825,10 +24828,10 @@
         <v>79</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>79</v>
+        <v>408</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>79</v>
@@ -24839,10 +24842,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>560</v>
+        <v>588</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24862,19 +24865,23 @@
         <v>79</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K183" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>106</v>
+        <v>460</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N183" s="2"/>
-      <c r="O183" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>79</v>
       </c>
@@ -24922,7 +24929,7 @@
         <v>79</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>108</v>
+        <v>464</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -24931,10 +24938,10 @@
         <v>91</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>79</v>
@@ -24943,10 +24950,10 @@
         <v>79</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>109</v>
+        <v>466</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>79</v>
@@ -24957,12 +24964,14 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C184" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>667</v>
+      </c>
       <c r="D184" t="s" s="2">
         <v>79</v>
       </c>
@@ -24971,7 +24980,7 @@
         <v>80</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>79</v>
@@ -24980,19 +24989,23 @@
         <v>79</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>112</v>
+        <v>338</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>201</v>
+        <v>668</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N184" s="2"/>
-      <c r="O184" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P184" t="s" s="2">
         <v>79</v>
       </c>
@@ -25016,31 +25029,31 @@
         <v>79</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>79</v>
+        <v>540</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>79</v>
+        <v>541</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB184" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC184" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE184" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>119</v>
+        <v>535</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -25049,10 +25062,10 @@
         <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>79</v>
@@ -25061,16 +25074,16 @@
         <v>79</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>79</v>
+        <v>543</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>79</v>
+        <v>544</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AP184" t="s" s="2">
-        <v>79</v>
+        <v>545</v>
       </c>
     </row>
     <row r="185" hidden="true">
@@ -25078,7 +25091,7 @@
         <v>669</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25086,7 +25099,7 @@
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G185" t="s" s="2">
         <v>91</v>
@@ -25101,24 +25114,22 @@
         <v>79</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>565</v>
+        <v>79</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>79</v>
@@ -25160,10 +25171,10 @@
         <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>91</v>
@@ -25184,7 +25195,7 @@
         <v>79</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>79</v>
@@ -25198,7 +25209,7 @@
         <v>670</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25206,10 +25217,10 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>79</v>
@@ -25221,13 +25232,13 @@
         <v>79</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>568</v>
+        <v>202</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -25239,7 +25250,7 @@
         <v>79</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>662</v>
+        <v>79</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>79</v>
@@ -25254,41 +25265,43 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="Y186" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z186" t="s" s="2">
-        <v>569</v>
+        <v>79</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB186" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC186" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE186" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>234</v>
+        <v>119</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>79</v>
@@ -25300,7 +25313,7 @@
         <v>79</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>79</v>
@@ -25314,18 +25327,20 @@
         <v>671</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C187" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="D187" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>79</v>
@@ -25334,23 +25349,19 @@
         <v>79</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>154</v>
+        <v>556</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>403</v>
+        <v>557</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N187" s="2"/>
+      <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>79</v>
       </c>
@@ -25398,7 +25409,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>407</v>
+        <v>119</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25410,7 +25421,7 @@
         <v>208</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>79</v>
@@ -25419,10 +25430,10 @@
         <v>79</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>408</v>
+        <v>79</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25436,7 +25447,7 @@
         <v>672</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25450,29 +25461,25 @@
         <v>91</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K188" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>460</v>
+        <v>106</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N188" s="2"/>
+      <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>79</v>
       </c>
@@ -25520,7 +25527,7 @@
         <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>464</v>
+        <v>108</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -25529,10 +25536,10 @@
         <v>91</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>79</v>
@@ -25541,10 +25548,10 @@
         <v>79</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>466</v>
+        <v>109</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25558,7 +25565,7 @@
         <v>673</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>673</v>
+        <v>562</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25569,32 +25576,28 @@
         <v>80</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I189" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>674</v>
+        <v>201</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>677</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N189" s="2"/>
+      <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
         <v>79</v>
       </c>
@@ -25630,46 +25633,46 @@
         <v>79</v>
       </c>
       <c r="AB189" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC189" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD189" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE189" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>673</v>
+        <v>119</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>310</v>
+        <v>208</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>678</v>
+        <v>79</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>679</v>
+        <v>79</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>680</v>
+        <v>79</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>681</v>
+        <v>79</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>682</v>
+        <v>79</v>
       </c>
       <c r="AP189" t="s" s="2">
         <v>79</v>
@@ -25677,10 +25680,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>683</v>
+        <v>564</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25688,13 +25691,13 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>79</v>
@@ -25703,26 +25706,24 @@
         <v>79</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>684</v>
+        <v>224</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>685</v>
+        <v>225</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>687</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>79</v>
+        <v>565</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>79</v>
@@ -25764,31 +25765,31 @@
         <v>79</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>683</v>
+        <v>228</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>688</v>
+        <v>79</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>689</v>
+        <v>79</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>681</v>
+        <v>199</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>79</v>
@@ -25799,10 +25800,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>690</v>
+        <v>567</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25813,10 +25814,10 @@
         <v>80</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>79</v>
@@ -25825,20 +25826,16 @@
         <v>79</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>691</v>
+        <v>176</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>692</v>
+        <v>232</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>695</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="N191" s="2"/>
+      <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>79</v>
       </c>
@@ -25847,7 +25844,7 @@
         <v>79</v>
       </c>
       <c r="S191" t="s" s="2">
-        <v>79</v>
+        <v>667</v>
       </c>
       <c r="T191" t="s" s="2">
         <v>79</v>
@@ -25862,56 +25859,56 @@
         <v>79</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>79</v>
+        <v>569</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="AC191" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>690</v>
+        <v>234</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>697</v>
+        <v>103</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>698</v>
+        <v>79</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>699</v>
+        <v>79</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>700</v>
+        <v>79</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>701</v>
+        <v>199</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>702</v>
+        <v>79</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>79</v>
@@ -25919,10 +25916,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>703</v>
+        <v>676</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>703</v>
+        <v>571</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25933,7 +25930,7 @@
         <v>80</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>79</v>
@@ -25942,19 +25939,23 @@
         <v>79</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>106</v>
+        <v>403</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N192" s="2"/>
-      <c r="O192" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P192" t="s" s="2">
         <v>79</v>
       </c>
@@ -26002,19 +26003,19 @@
         <v>79</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>108</v>
+        <v>407</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>79</v>
@@ -26023,10 +26024,10 @@
         <v>79</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>79</v>
+        <v>408</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>109</v>
+        <v>409</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>79</v>
@@ -26037,44 +26038,46 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>704</v>
+        <v>677</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>704</v>
+        <v>588</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H193" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I193" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>113</v>
+        <v>460</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>114</v>
+        <v>461</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O193" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>79</v>
       </c>
@@ -26110,31 +26113,31 @@
         <v>79</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>119</v>
+        <v>464</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>79</v>
@@ -26143,10 +26146,10 @@
         <v>79</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>109</v>
+        <v>466</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>79</v>
@@ -26157,14 +26160,12 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>705</v>
+        <v>678</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>706</v>
-      </c>
+        <v>678</v>
+      </c>
+      <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
         <v>79</v>
       </c>
@@ -26176,25 +26177,29 @@
         <v>91</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>707</v>
+        <v>105</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>708</v>
+        <v>679</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>682</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>79</v>
       </c>
@@ -26242,34 +26247,34 @@
         <v>79</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>119</v>
+        <v>678</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>79</v>
+        <v>683</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>79</v>
+        <v>684</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>79</v>
+        <v>685</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>79</v>
+        <v>686</v>
       </c>
       <c r="AO194" t="s" s="2">
-        <v>79</v>
+        <v>687</v>
       </c>
       <c r="AP194" t="s" s="2">
         <v>79</v>
@@ -26277,10 +26282,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>710</v>
+        <v>688</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>710</v>
+        <v>688</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26288,31 +26293,35 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H195" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J195" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>711</v>
+        <v>689</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="N195" s="2"/>
-      <c r="O195" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="O195" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="P195" t="s" s="2">
         <v>79</v>
       </c>
@@ -26336,13 +26345,13 @@
         <v>79</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>713</v>
+        <v>79</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>714</v>
+        <v>79</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>79</v>
@@ -26360,34 +26369,34 @@
         <v>79</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>715</v>
+        <v>688</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>716</v>
+        <v>79</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>79</v>
+        <v>693</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>79</v>
+        <v>694</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>717</v>
+        <v>79</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>718</v>
+        <v>686</v>
       </c>
       <c r="AO195" t="s" s="2">
-        <v>719</v>
+        <v>79</v>
       </c>
       <c r="AP195" t="s" s="2">
         <v>79</v>
@@ -26395,10 +26404,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26406,34 +26415,34 @@
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H196" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J196" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>105</v>
+        <v>696</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>721</v>
+        <v>697</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>722</v>
+        <v>698</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>723</v>
+        <v>699</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>724</v>
+        <v>700</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>79</v>
@@ -26470,46 +26479,44 @@
         <v>79</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="AC196" s="2"/>
       <c r="AD196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>103</v>
+        <v>702</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>79</v>
+        <v>703</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>79</v>
+        <v>704</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>727</v>
+        <v>706</v>
       </c>
       <c r="AO196" t="s" s="2">
-        <v>369</v>
+        <v>707</v>
       </c>
       <c r="AP196" t="s" s="2">
         <v>79</v>
@@ -26517,10 +26524,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26537,26 +26544,22 @@
         <v>79</v>
       </c>
       <c r="I197" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J197" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>729</v>
+        <v>106</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N197" s="2"/>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>79</v>
       </c>
@@ -26580,13 +26583,13 @@
         <v>79</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>733</v>
+        <v>79</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>734</v>
+        <v>79</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>79</v>
@@ -26604,7 +26607,7 @@
         <v>79</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>735</v>
+        <v>108</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26616,7 +26619,7 @@
         <v>79</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>79</v>
@@ -26625,13 +26628,13 @@
         <v>79</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>736</v>
+        <v>79</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>737</v>
+        <v>109</v>
       </c>
       <c r="AO197" t="s" s="2">
-        <v>738</v>
+        <v>79</v>
       </c>
       <c r="AP197" t="s" s="2">
         <v>79</v>
@@ -26639,21 +26642,21 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>79</v>
@@ -26662,19 +26665,19 @@
         <v>79</v>
       </c>
       <c r="J198" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>740</v>
+        <v>112</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>741</v>
+        <v>113</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>742</v>
+        <v>114</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>743</v>
+        <v>115</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26712,31 +26715,31 @@
         <v>79</v>
       </c>
       <c r="AB198" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC198" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE198" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>744</v>
+        <v>119</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK198" t="s" s="2">
         <v>79</v>
@@ -26745,7 +26748,7 @@
         <v>79</v>
       </c>
       <c r="AM198" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AN198" t="s" s="2">
         <v>109</v>
@@ -26759,12 +26762,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>745</v>
+        <v>710</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C199" s="2"/>
+        <v>709</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>711</v>
+      </c>
       <c r="D199" t="s" s="2">
         <v>79</v>
       </c>
@@ -26782,16 +26787,16 @@
         <v>79</v>
       </c>
       <c r="J199" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>231</v>
+        <v>712</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>746</v>
+        <v>713</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>747</v>
+        <v>714</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26842,19 +26847,19 @@
         <v>79</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>748</v>
+        <v>119</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI199" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>79</v>
@@ -26863,13 +26868,13 @@
         <v>79</v>
       </c>
       <c r="AM199" t="s" s="2">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>749</v>
+        <v>79</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>79</v>
@@ -26877,23 +26882,21 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>750</v>
+        <v>715</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="C200" t="s" s="2">
-        <v>751</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>79</v>
@@ -26902,23 +26905,19 @@
         <v>79</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>752</v>
+        <v>176</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>753</v>
+        <v>716</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>695</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>79</v>
       </c>
@@ -26942,13 +26941,13 @@
         <v>79</v>
       </c>
       <c r="X200" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>79</v>
+        <v>718</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>79</v>
+        <v>719</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>79</v>
@@ -26966,34 +26965,34 @@
         <v>79</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>208</v>
+        <v>721</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>697</v>
+        <v>103</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>754</v>
+        <v>79</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>755</v>
+        <v>79</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>700</v>
+        <v>722</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>701</v>
+        <v>723</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>702</v>
+        <v>724</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>79</v>
@@ -27001,10 +27000,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>756</v>
+        <v>725</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>756</v>
+        <v>725</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27012,34 +27011,34 @@
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H201" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I201" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J201" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I201" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J201" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K201" t="s" s="2">
-        <v>757</v>
+        <v>105</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>758</v>
+        <v>726</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>759</v>
+        <v>727</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>760</v>
+        <v>728</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>761</v>
+        <v>729</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>79</v>
@@ -27088,34 +27087,34 @@
         <v>79</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>756</v>
+        <v>730</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>762</v>
+        <v>103</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>763</v>
+        <v>79</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>764</v>
+        <v>79</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>765</v>
+        <v>731</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>766</v>
+        <v>732</v>
       </c>
       <c r="AO201" t="s" s="2">
-        <v>767</v>
+        <v>369</v>
       </c>
       <c r="AP201" t="s" s="2">
         <v>79</v>
@@ -27123,10 +27122,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>768</v>
+        <v>733</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>768</v>
+        <v>733</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27143,23 +27142,25 @@
         <v>79</v>
       </c>
       <c r="I202" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J202" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>769</v>
+        <v>176</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>770</v>
+        <v>734</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="N202" s="2"/>
+        <v>735</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>736</v>
+      </c>
       <c r="O202" t="s" s="2">
-        <v>772</v>
+        <v>737</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>79</v>
@@ -27184,13 +27185,13 @@
         <v>79</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>79</v>
+        <v>738</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>79</v>
+        <v>739</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>79</v>
@@ -27208,7 +27209,7 @@
         <v>79</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>768</v>
+        <v>740</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -27229,13 +27230,13 @@
         <v>79</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>531</v>
+        <v>741</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>773</v>
+        <v>742</v>
       </c>
       <c r="AO202" t="s" s="2">
-        <v>109</v>
+        <v>743</v>
       </c>
       <c r="AP202" t="s" s="2">
         <v>79</v>
@@ -27243,10 +27244,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>774</v>
+        <v>744</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>774</v>
+        <v>744</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27266,18 +27267,20 @@
         <v>79</v>
       </c>
       <c r="J203" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>105</v>
+        <v>745</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>106</v>
+        <v>746</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N203" s="2"/>
+        <v>747</v>
+      </c>
+      <c r="N203" t="s" s="2">
+        <v>748</v>
+      </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
         <v>79</v>
@@ -27326,7 +27329,7 @@
         <v>79</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>108</v>
+        <v>749</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -27338,7 +27341,7 @@
         <v>79</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>79</v>
@@ -27347,7 +27350,7 @@
         <v>79</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AN203" t="s" s="2">
         <v>109</v>
@@ -27361,21 +27364,21 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>775</v>
+        <v>750</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>79</v>
@@ -27384,20 +27387,18 @@
         <v>79</v>
       </c>
       <c r="J204" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>112</v>
+        <v>231</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>113</v>
+        <v>751</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>752</v>
+      </c>
+      <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>79</v>
@@ -27434,31 +27435,31 @@
         <v>79</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>119</v>
+        <v>753</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>79</v>
@@ -27467,13 +27468,13 @@
         <v>79</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>109</v>
+        <v>754</v>
       </c>
       <c r="AO204" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="AP204" t="s" s="2">
         <v>79</v>
@@ -27481,12 +27482,14 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="C205" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>756</v>
+      </c>
       <c r="D205" t="s" s="2">
         <v>79</v>
       </c>
@@ -27495,7 +27498,7 @@
         <v>80</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>79</v>
@@ -27504,21 +27507,23 @@
         <v>79</v>
       </c>
       <c r="J205" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>105</v>
+        <v>757</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>778</v>
+        <v>698</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="O205" s="2"/>
+        <v>699</v>
+      </c>
+      <c r="O205" t="s" s="2">
+        <v>700</v>
+      </c>
       <c r="P205" t="s" s="2">
         <v>79</v>
       </c>
@@ -27566,34 +27571,34 @@
         <v>79</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>780</v>
+        <v>695</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>781</v>
+        <v>208</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>103</v>
+        <v>702</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>79</v>
+        <v>759</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>79</v>
+        <v>760</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>79</v>
+        <v>705</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>199</v>
+        <v>706</v>
       </c>
       <c r="AO205" t="s" s="2">
-        <v>79</v>
+        <v>707</v>
       </c>
       <c r="AP205" t="s" s="2">
         <v>79</v>
@@ -27601,10 +27606,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27615,30 +27620,32 @@
         <v>80</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H206" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>138</v>
+        <v>762</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>783</v>
+        <v>763</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>784</v>
+        <v>764</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="O206" s="2"/>
+        <v>765</v>
+      </c>
+      <c r="O206" t="s" s="2">
+        <v>766</v>
+      </c>
       <c r="P206" t="s" s="2">
         <v>79</v>
       </c>
@@ -27662,11 +27669,13 @@
         <v>79</v>
       </c>
       <c r="X206" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y206" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y206" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z206" t="s" s="2">
-        <v>549</v>
+        <v>79</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>79</v>
@@ -27684,34 +27693,34 @@
         <v>79</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>786</v>
+        <v>761</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>103</v>
+        <v>767</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>79</v>
+        <v>768</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>79</v>
+        <v>769</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>79</v>
+        <v>770</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>199</v>
+        <v>771</v>
       </c>
       <c r="AO206" t="s" s="2">
-        <v>79</v>
+        <v>772</v>
       </c>
       <c r="AP206" t="s" s="2">
         <v>79</v>
@@ -27719,10 +27728,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27745,18 +27754,18 @@
         <v>92</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>304</v>
+        <v>774</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="O207" s="2"/>
+        <v>776</v>
+      </c>
+      <c r="N207" s="2"/>
+      <c r="O207" t="s" s="2">
+        <v>777</v>
+      </c>
       <c r="P207" t="s" s="2">
         <v>79</v>
       </c>
@@ -27804,7 +27813,7 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>791</v>
+        <v>773</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27825,13 +27834,13 @@
         <v>79</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>79</v>
+        <v>531</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="AO207" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AP207" t="s" s="2">
         <v>79</v>
@@ -27839,10 +27848,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27862,20 +27871,18 @@
         <v>79</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K208" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>794</v>
+        <v>106</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>796</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>79</v>
@@ -27924,7 +27931,7 @@
         <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>797</v>
+        <v>108</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -27936,7 +27943,7 @@
         <v>79</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>79</v>
@@ -27948,7 +27955,7 @@
         <v>79</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>79</v>
@@ -27959,14 +27966,14 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
@@ -27985,20 +27992,18 @@
         <v>79</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>799</v>
+        <v>112</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>800</v>
+        <v>113</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>801</v>
+        <v>114</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>803</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>79</v>
       </c>
@@ -28034,19 +28039,19 @@
         <v>79</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>798</v>
+        <v>119</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -28058,7 +28063,7 @@
         <v>79</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>79</v>
@@ -28070,7 +28075,7 @@
         <v>79</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>804</v>
+        <v>109</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>79</v>
@@ -28081,10 +28086,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>805</v>
+        <v>781</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>805</v>
+        <v>781</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28104,18 +28109,20 @@
         <v>79</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K210" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>106</v>
+        <v>782</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N210" s="2"/>
+        <v>783</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>784</v>
+      </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>79</v>
@@ -28164,7 +28171,7 @@
         <v>79</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>108</v>
+        <v>785</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -28173,10 +28180,10 @@
         <v>91</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>79</v>
+        <v>786</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>79</v>
@@ -28188,7 +28195,7 @@
         <v>79</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>79</v>
@@ -28199,21 +28206,21 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>79</v>
@@ -28222,19 +28229,19 @@
         <v>79</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>113</v>
+        <v>788</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>114</v>
+        <v>789</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>115</v>
+        <v>790</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -28260,13 +28267,11 @@
         <v>79</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y211" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>79</v>
+        <v>549</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>79</v>
@@ -28284,19 +28289,19 @@
         <v>79</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>119</v>
+        <v>791</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>79</v>
@@ -28308,7 +28313,7 @@
         <v>79</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>79</v>
@@ -28319,46 +28324,44 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>808</v>
+        <v>79</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I212" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J212" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>112</v>
+        <v>304</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O212" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>79</v>
       </c>
@@ -28406,19 +28409,19 @@
         <v>79</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>79</v>
@@ -28430,7 +28433,7 @@
         <v>79</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>199</v>
+        <v>797</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>79</v>
@@ -28441,10 +28444,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28464,21 +28467,21 @@
         <v>79</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>338</v>
+        <v>105</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>813</v>
+        <v>799</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="N213" s="2"/>
-      <c r="O213" t="s" s="2">
-        <v>815</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>79</v>
       </c>
@@ -28502,13 +28505,13 @@
         <v>79</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>158</v>
+        <v>79</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>816</v>
+        <v>79</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>817</v>
+        <v>79</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>79</v>
@@ -28526,7 +28529,7 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28550,7 +28553,7 @@
         <v>79</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>818</v>
+        <v>199</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>79</v>
@@ -28561,10 +28564,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>819</v>
+        <v>803</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>819</v>
+        <v>803</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28575,7 +28578,7 @@
         <v>80</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>79</v>
@@ -28587,17 +28590,19 @@
         <v>79</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>820</v>
+        <v>804</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="N214" s="2"/>
+        <v>806</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>807</v>
+      </c>
       <c r="O214" t="s" s="2">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>79</v>
@@ -28646,13 +28651,13 @@
         <v>79</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>819</v>
+        <v>803</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>79</v>
@@ -28667,10 +28672,10 @@
         <v>79</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>824</v>
+        <v>79</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>825</v>
+        <v>809</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>79</v>
@@ -28681,10 +28686,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28695,7 +28700,7 @@
         <v>80</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>79</v>
@@ -28707,18 +28712,16 @@
         <v>79</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>691</v>
+        <v>105</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>827</v>
+        <v>106</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>693</v>
+        <v>107</v>
       </c>
       <c r="N215" s="2"/>
-      <c r="O215" t="s" s="2">
-        <v>828</v>
-      </c>
+      <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>79</v>
       </c>
@@ -28766,19 +28769,19 @@
         <v>79</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>826</v>
+        <v>108</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>829</v>
+        <v>79</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>79</v>
@@ -28787,13 +28790,13 @@
         <v>79</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>700</v>
+        <v>79</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>701</v>
+        <v>109</v>
       </c>
       <c r="AO215" t="s" s="2">
-        <v>702</v>
+        <v>79</v>
       </c>
       <c r="AP215" t="s" s="2">
         <v>79</v>
@@ -28801,21 +28804,21 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>830</v>
+        <v>811</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>830</v>
+        <v>811</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>79</v>
@@ -28827,20 +28830,18 @@
         <v>79</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>831</v>
+        <v>112</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>832</v>
+        <v>113</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>759</v>
+        <v>114</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>833</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>79</v>
       </c>
@@ -28888,19 +28889,19 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>830</v>
+        <v>119</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>79</v>
@@ -28909,13 +28910,13 @@
         <v>79</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>765</v>
+        <v>79</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>766</v>
+        <v>109</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>767</v>
+        <v>79</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>79</v>
@@ -28923,14 +28924,14 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>834</v>
+        <v>812</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>834</v>
+        <v>812</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
-        <v>79</v>
+        <v>813</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
@@ -28940,26 +28941,28 @@
         <v>81</v>
       </c>
       <c r="H217" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I217" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I217" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="J217" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>835</v>
+        <v>112</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>836</v>
+        <v>814</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="N217" s="2"/>
+        <v>815</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O217" t="s" s="2">
-        <v>838</v>
+        <v>301</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>79</v>
@@ -29008,7 +29011,7 @@
         <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>834</v>
+        <v>816</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -29020,29 +29023,631 @@
         <v>79</v>
       </c>
       <c r="AJ217" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK217" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL217" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM217" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN217" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AO217" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP217" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="218" hidden="true">
+      <c r="A218" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="C218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G218" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K218" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="N218" s="2"/>
+      <c r="O218" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="P218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q218" s="2"/>
+      <c r="R218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X218" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y218" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="Z218" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="AA218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF218" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="AG218" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH218" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ218" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK217" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL217" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM217" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN217" t="s" s="2">
+      <c r="AK218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN218" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AO218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP218" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="219" hidden="true">
+      <c r="A219" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="C219" s="2"/>
+      <c r="D219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E219" s="2"/>
+      <c r="F219" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G219" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K219" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="L219" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="M219" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="N219" s="2"/>
+      <c r="O219" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="P219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q219" s="2"/>
+      <c r="R219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF219" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="AG219" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH219" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ219" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM219" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="AN219" t="s" s="2">
+        <v>830</v>
+      </c>
+      <c r="AO219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP219" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="220" hidden="true">
+      <c r="A220" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="C220" s="2"/>
+      <c r="D220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E220" s="2"/>
+      <c r="F220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G220" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K220" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="L220" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="M220" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N220" s="2"/>
+      <c r="O220" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="P220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q220" s="2"/>
+      <c r="R220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF220" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="AG220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH220" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI220" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AJ220" t="s" s="2">
+        <v>834</v>
+      </c>
+      <c r="AK220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM220" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AN220" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AO220" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AP220" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="221" hidden="true">
+      <c r="A221" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="C221" s="2"/>
+      <c r="D221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E221" s="2"/>
+      <c r="F221" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G221" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K221" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="L221" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="M221" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="O221" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="P221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q221" s="2"/>
+      <c r="R221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF221" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="AG221" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH221" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI221" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AJ221" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM221" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="AN221" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="AO221" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="AP221" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="222" hidden="true">
+      <c r="A222" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="C222" s="2"/>
+      <c r="D222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G222" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H222" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K222" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="L222" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="N222" s="2"/>
+      <c r="O222" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="P222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q222" s="2"/>
+      <c r="R222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF222" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="AG222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH222" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ222" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN222" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="AO217" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP217" t="s" s="2">
+      <c r="AO222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP222" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP217">
+  <autoFilter ref="A1:AP222">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -29052,7 +29657,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI216">
+  <conditionalFormatting sqref="A2:AI221">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
